--- a/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>ORBT</t>
   </si>
@@ -656,332 +656,361 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="E7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44469</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>44104</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="T7" s="2">
         <v>43555</v>
       </c>
-      <c r="R7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="V7" s="2">
         <v>43373</v>
       </c>
-      <c r="T7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2">
+      <c r="X7" s="2">
         <v>43190</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Z7" s="2">
         <v>43008</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AA7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AB7" s="2">
         <v>42825</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AC7" s="2">
         <v>42735</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AD7" s="2">
         <v>42643</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AE7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F8" s="3">
+        <v>6000</v>
+      </c>
+      <c r="G8" s="3">
         <v>5800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="H8" s="3">
         <v>6800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
         <v>5000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>6100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="K8" s="3">
         <v>5800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>5400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>6400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>7900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>5800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>5900</v>
-      </c>
-      <c r="N8" s="3">
-        <v>6500</v>
-      </c>
-      <c r="O8" s="3">
-        <v>6100</v>
-      </c>
-      <c r="P8" s="3">
-        <v>6900</v>
       </c>
       <c r="Q8" s="3">
         <v>6500</v>
       </c>
       <c r="R8" s="3">
+        <v>6100</v>
+      </c>
+      <c r="S8" s="3">
+        <v>6900</v>
+      </c>
+      <c r="T8" s="3">
+        <v>6500</v>
+      </c>
+      <c r="U8" s="3">
         <v>24700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="V8" s="3">
         <v>6300</v>
-      </c>
-      <c r="T8" s="3">
-        <v>5000</v>
-      </c>
-      <c r="U8" s="3">
-        <v>5300</v>
-      </c>
-      <c r="V8" s="3">
-        <v>20900</v>
       </c>
       <c r="W8" s="3">
         <v>5000</v>
       </c>
       <c r="X8" s="3">
+        <v>5300</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>20900</v>
+      </c>
+      <c r="Z8" s="3">
         <v>5000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AB8" s="3">
         <v>5200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AC8" s="3">
         <v>5500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AD8" s="3">
         <v>5500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AE8" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="G9" s="3">
         <v>4200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="H9" s="3">
         <v>4300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="I9" s="3">
         <v>3000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="J9" s="3">
         <v>3800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="K9" s="3">
         <v>3600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="L9" s="3">
         <v>3700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <v>4700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>5400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>4700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>4100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="Q9" s="3">
         <v>4900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="R9" s="3">
         <v>4300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="S9" s="3">
         <v>4700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="T9" s="3">
         <v>4800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="U9" s="3">
         <v>16500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="V9" s="3">
         <v>4100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="W9" s="3">
         <v>3300</v>
-      </c>
-      <c r="U9" s="3">
-        <v>3200</v>
-      </c>
-      <c r="V9" s="3">
-        <v>12700</v>
-      </c>
-      <c r="W9" s="3">
-        <v>2900</v>
       </c>
       <c r="X9" s="3">
         <v>3200</v>
       </c>
       <c r="Y9" s="3">
+        <v>12700</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AA9" s="3">
         <v>3200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AC9" s="3">
         <v>3300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AD9" s="3">
         <v>3500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AE9" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G10" s="3">
         <v>1600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="H10" s="3">
         <v>2500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="I10" s="3">
         <v>2000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="J10" s="3">
         <v>2300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="K10" s="3">
         <v>2200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="L10" s="3">
         <v>1700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="M10" s="3">
         <v>1700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="N10" s="3">
         <v>2500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="O10" s="3">
         <v>1100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="P10" s="3">
         <v>1800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="Q10" s="3">
         <v>1600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="R10" s="3">
         <v>1800</v>
-      </c>
-      <c r="P10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="R10" s="3">
-        <v>8200</v>
       </c>
       <c r="S10" s="3">
         <v>2200</v>
@@ -990,31 +1019,40 @@
         <v>1700</v>
       </c>
       <c r="U10" s="3">
+        <v>8200</v>
+      </c>
+      <c r="V10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="W10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X10" s="3">
         <v>2100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Y10" s="3">
         <v>8200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Z10" s="3">
         <v>2100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AA10" s="3">
         <v>1800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AB10" s="3">
         <v>2000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AC10" s="3">
         <v>2200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AD10" s="3">
         <v>2000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AE10" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1081,11 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1164,17 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,56 +1253,65 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-1600</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1262,29 +1321,38 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1363,8 +1431,17 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1467,189 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>7100</v>
+      </c>
+      <c r="F17" s="3">
         <v>6300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="H17" s="3">
         <v>6400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="I17" s="3">
         <v>4800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="J17" s="3">
         <v>5400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="K17" s="3">
         <v>5200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>3500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>6200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>7000</v>
-      </c>
-      <c r="L17" s="3">
-        <v>6100</v>
-      </c>
-      <c r="M17" s="3">
-        <v>5800</v>
-      </c>
-      <c r="N17" s="3">
-        <v>6700</v>
       </c>
       <c r="O17" s="3">
         <v>6100</v>
       </c>
       <c r="P17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="R17" s="3">
+        <v>6100</v>
+      </c>
+      <c r="S17" s="3">
         <v>6300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>6400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="U17" s="3">
         <v>23000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="V17" s="3">
         <v>5700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="W17" s="3">
         <v>4800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="X17" s="3">
         <v>4900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Y17" s="3">
         <v>19300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>4600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AA17" s="3">
         <v>4800</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>4900</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>5000</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>5100</v>
       </c>
       <c r="AB17" s="3">
         <v>4900</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>5100</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>4900</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-500</v>
+        <v>-1200</v>
       </c>
       <c r="E18" s="3">
         <v>400</v>
       </c>
       <c r="F18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H18" s="3">
+        <v>400</v>
+      </c>
+      <c r="I18" s="3">
         <v>200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
         <v>600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="Q18" s="3">
         <v>-200</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>100</v>
-      </c>
       <c r="R18" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="S18" s="3">
         <v>600</v>
       </c>
       <c r="T18" s="3">
+        <v>100</v>
+      </c>
+      <c r="U18" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V18" s="3">
+        <v>600</v>
+      </c>
+      <c r="W18" s="3">
         <v>200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Y18" s="3">
         <v>1600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Z18" s="3">
         <v>400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AA18" s="3">
         <v>200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AB18" s="3">
         <v>300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AC18" s="3">
         <v>500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AD18" s="3">
         <v>400</v>
       </c>
-      <c r="AB18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,8 +1678,11 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1589,16 +1690,16 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1607,23 +1708,23 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1640,17 +1741,17 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1660,65 +1761,74 @@
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>-300</v>
+      <c r="D21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E21" s="3">
+        <v>800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H21" s="3">
+        <v>500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>700</v>
+      </c>
+      <c r="K21" s="3">
         <v>600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="L21" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3">
-        <v>700</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="N21" s="3">
+        <v>900</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>600</v>
       </c>
-      <c r="I21" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>900</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-400</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="T21" s="3">
         <v>100</v>
       </c>
-      <c r="N21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>100</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="U21" s="3">
         <v>1800</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1740,8 +1850,17 @@
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1751,17 +1870,17 @@
       <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1769,11 +1888,11 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1781,11 +1900,11 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1793,11 +1912,11 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1805,8 +1924,8 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -1820,88 +1939,106 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>700</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G23" s="3">
         <v>-400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="I23" s="3">
         <v>200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3">
         <v>600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>-200</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>100</v>
-      </c>
       <c r="R23" s="3">
-        <v>1700</v>
+        <v>0</v>
       </c>
       <c r="S23" s="3">
         <v>600</v>
       </c>
       <c r="T23" s="3">
+        <v>100</v>
+      </c>
+      <c r="U23" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V23" s="3">
+        <v>600</v>
+      </c>
+      <c r="W23" s="3">
         <v>200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Y23" s="3">
         <v>1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Z23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AA23" s="3">
         <v>200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AB23" s="3">
         <v>300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AC23" s="3">
         <v>500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AD23" s="3">
         <v>400</v>
       </c>
-      <c r="AB23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1948,28 +2085,28 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>-500</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>-600</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-200</v>
-      </c>
-      <c r="W24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0</v>
       </c>
       <c r="Z24" s="3">
         <v>-300</v>
@@ -1980,8 +2117,17 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2206,195 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>700</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G26" s="3">
         <v>-400</v>
-      </c>
-      <c r="E26" s="3">
-        <v>500</v>
-      </c>
-      <c r="F26" s="3">
-        <v>200</v>
-      </c>
-      <c r="G26" s="3">
-        <v>700</v>
       </c>
       <c r="H26" s="3">
         <v>500</v>
       </c>
       <c r="I26" s="3">
+        <v>200</v>
+      </c>
+      <c r="J26" s="3">
+        <v>700</v>
+      </c>
+      <c r="K26" s="3">
+        <v>500</v>
+      </c>
+      <c r="L26" s="3">
         <v>1800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
       <c r="R26" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="S26" s="3">
         <v>600</v>
       </c>
       <c r="T26" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="U26" s="3">
-        <v>400</v>
+        <v>2200</v>
       </c>
       <c r="V26" s="3">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="W26" s="3">
         <v>700</v>
       </c>
       <c r="X26" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA26" s="3">
         <v>200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AB26" s="3">
         <v>300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AD26" s="3">
         <v>500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AE26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>700</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G27" s="3">
         <v>-400</v>
-      </c>
-      <c r="E27" s="3">
-        <v>500</v>
-      </c>
-      <c r="F27" s="3">
-        <v>200</v>
-      </c>
-      <c r="G27" s="3">
-        <v>700</v>
       </c>
       <c r="H27" s="3">
         <v>500</v>
       </c>
       <c r="I27" s="3">
+        <v>200</v>
+      </c>
+      <c r="J27" s="3">
+        <v>700</v>
+      </c>
+      <c r="K27" s="3">
+        <v>500</v>
+      </c>
+      <c r="L27" s="3">
         <v>1800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-200</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
       <c r="R27" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="S27" s="3">
         <v>600</v>
       </c>
       <c r="T27" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="U27" s="3">
-        <v>400</v>
+        <v>2200</v>
       </c>
       <c r="V27" s="3">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="W27" s="3">
         <v>700</v>
       </c>
       <c r="X27" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA27" s="3">
         <v>200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AB27" s="3">
         <v>300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AC27" s="3">
         <v>800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AD27" s="3">
         <v>500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AE27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2473,17 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2562,17 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2651,17 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,8 +2740,17 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2549,16 +2758,16 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -2567,23 +2776,23 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2600,17 +2809,17 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -2620,88 +2829,106 @@
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>700</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G33" s="3">
         <v>-400</v>
-      </c>
-      <c r="E33" s="3">
-        <v>500</v>
-      </c>
-      <c r="F33" s="3">
-        <v>200</v>
-      </c>
-      <c r="G33" s="3">
-        <v>700</v>
       </c>
       <c r="H33" s="3">
         <v>500</v>
       </c>
       <c r="I33" s="3">
+        <v>200</v>
+      </c>
+      <c r="J33" s="3">
+        <v>700</v>
+      </c>
+      <c r="K33" s="3">
+        <v>500</v>
+      </c>
+      <c r="L33" s="3">
         <v>1800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-200</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>100</v>
-      </c>
       <c r="R33" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="S33" s="3">
         <v>600</v>
       </c>
       <c r="T33" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="U33" s="3">
-        <v>400</v>
+        <v>2200</v>
       </c>
       <c r="V33" s="3">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="W33" s="3">
         <v>700</v>
       </c>
       <c r="X33" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA33" s="3">
         <v>200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AB33" s="3">
         <v>300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AC33" s="3">
         <v>800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AD33" s="3">
         <v>500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AE33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +3007,200 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>700</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G35" s="3">
         <v>-400</v>
-      </c>
-      <c r="E35" s="3">
-        <v>500</v>
-      </c>
-      <c r="F35" s="3">
-        <v>200</v>
-      </c>
-      <c r="G35" s="3">
-        <v>700</v>
       </c>
       <c r="H35" s="3">
         <v>500</v>
       </c>
       <c r="I35" s="3">
+        <v>200</v>
+      </c>
+      <c r="J35" s="3">
+        <v>700</v>
+      </c>
+      <c r="K35" s="3">
+        <v>500</v>
+      </c>
+      <c r="L35" s="3">
         <v>1800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-200</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>100</v>
-      </c>
       <c r="R35" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="S35" s="3">
         <v>600</v>
       </c>
       <c r="T35" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="U35" s="3">
-        <v>400</v>
+        <v>2200</v>
       </c>
       <c r="V35" s="3">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="W35" s="3">
         <v>700</v>
       </c>
       <c r="X35" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA35" s="3">
         <v>200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AB35" s="3">
         <v>300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AC35" s="3">
         <v>800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AD35" s="3">
         <v>500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AE35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="E38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44469</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>44104</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="T38" s="2">
         <v>43555</v>
       </c>
-      <c r="R38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="V38" s="2">
         <v>43373</v>
       </c>
-      <c r="T38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2">
+      <c r="X38" s="2">
         <v>43190</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Z38" s="2">
         <v>43008</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AA38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AB38" s="2">
         <v>42825</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AC38" s="2">
         <v>42735</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AD38" s="2">
         <v>42643</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AE38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3229,11 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,88 +3262,100 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F41" s="3">
         <v>4700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>9200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>8300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="L41" s="3">
         <v>7000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>7500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>5700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>4400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>2800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="Q41" s="3">
         <v>3600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="R41" s="3">
         <v>3900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="S41" s="3">
         <v>3600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="T41" s="3">
         <v>2900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="U41" s="3">
         <v>4500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="V41" s="3">
         <v>1600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="W41" s="3">
         <v>1100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="X41" s="3">
         <v>900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Y41" s="3">
         <v>900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Z41" s="3">
         <v>800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AA41" s="3">
         <v>2400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AB41" s="3">
         <v>1900</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3145,205 +3414,232 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Z42" s="3">
         <v>300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="AA42" s="3">
         <v>200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AB42" s="3">
         <v>200</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3100</v>
+        <v>4300</v>
       </c>
       <c r="E43" s="3">
-        <v>3600</v>
+        <v>4000</v>
       </c>
       <c r="F43" s="3">
         <v>3100</v>
       </c>
       <c r="G43" s="3">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="H43" s="3">
-        <v>3700</v>
+        <v>3100</v>
       </c>
       <c r="I43" s="3">
         <v>3300</v>
       </c>
       <c r="J43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L43" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M43" s="3">
         <v>3400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>4000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>3700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>3800</v>
-      </c>
-      <c r="N43" s="3">
-        <v>3800</v>
-      </c>
-      <c r="O43" s="3">
-        <v>3800</v>
-      </c>
-      <c r="P43" s="3">
-        <v>3700</v>
       </c>
       <c r="Q43" s="3">
         <v>3800</v>
       </c>
       <c r="R43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="S43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="T43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U43" s="3">
         <v>2400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="V43" s="3">
         <v>3600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="W43" s="3">
         <v>3700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="X43" s="3">
         <v>4300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Y43" s="3">
         <v>3300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Z43" s="3">
         <v>3000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AA43" s="3">
         <v>2700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AB43" s="3">
         <v>3000</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F44" s="3">
         <v>11100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>11800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>8500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>8400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>9000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
+        <v>9000</v>
+      </c>
+      <c r="L44" s="3">
         <v>9400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>9400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>10000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>10800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>11200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="Q44" s="3">
         <v>10500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="R44" s="3">
         <v>10300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="S44" s="3">
         <v>10000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="T44" s="3">
         <v>10700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="U44" s="3">
         <v>10100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="V44" s="3">
         <v>11400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="W44" s="3">
         <v>10900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="X44" s="3">
         <v>9600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Y44" s="3">
         <v>10100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Z44" s="3">
         <v>10000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="AA44" s="3">
         <v>10000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AB44" s="3">
         <v>10000</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="3">
         <v>600</v>
-      </c>
-      <c r="E45" s="3">
-        <v>400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>400</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
       </c>
       <c r="H45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I45" s="3">
         <v>400</v>
@@ -3352,141 +3648,159 @@
         <v>300</v>
       </c>
       <c r="K45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L45" s="3">
         <v>400</v>
       </c>
       <c r="M45" s="3">
+        <v>300</v>
+      </c>
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="N45" s="3">
-        <v>300</v>
-      </c>
       <c r="O45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="P45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="Q45" s="3">
         <v>300</v>
       </c>
       <c r="R45" s="3">
+        <v>500</v>
+      </c>
+      <c r="S45" s="3">
+        <v>200</v>
+      </c>
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
+        <v>300</v>
+      </c>
+      <c r="W45" s="3">
         <v>900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="X45" s="3">
         <v>1200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Y45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="AA45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AB45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>19000</v>
+      </c>
+      <c r="F46" s="3">
         <v>19400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>21100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>21300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>20400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>19800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
+        <v>19800</v>
+      </c>
+      <c r="L46" s="3">
         <v>20100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>20600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>20100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>19300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>18200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="Q46" s="3">
         <v>18200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="R46" s="3">
         <v>18500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="S46" s="3">
         <v>17400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="T46" s="3">
         <v>17600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="U46" s="3">
         <v>17400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="V46" s="3">
         <v>16900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="W46" s="3">
         <v>16500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="X46" s="3">
         <v>15900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Y46" s="3">
         <v>14700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Z46" s="3">
         <v>14400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="AA46" s="3">
         <v>15300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AB46" s="3">
         <v>15400</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3565,102 +3879,120 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F48" s="3">
         <v>3500</v>
-      </c>
-      <c r="E48" s="3">
-        <v>3400</v>
-      </c>
-      <c r="F48" s="3">
-        <v>3300</v>
       </c>
       <c r="G48" s="3">
         <v>3400</v>
       </c>
       <c r="H48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J48" s="3">
         <v>3600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L48" s="3">
         <v>700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>1000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>1100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>1100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="Q48" s="3">
         <v>1200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="R48" s="3">
         <v>1300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="S48" s="3">
         <v>1400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="T48" s="3">
         <v>1500</v>
-      </c>
-      <c r="R48" s="3">
-        <v>300</v>
-      </c>
-      <c r="S48" s="3">
-        <v>300</v>
-      </c>
-      <c r="T48" s="3">
-        <v>300</v>
       </c>
       <c r="U48" s="3">
         <v>300</v>
       </c>
       <c r="V48" s="3">
+        <v>300</v>
+      </c>
+      <c r="W48" s="3">
+        <v>300</v>
+      </c>
+      <c r="X48" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y48" s="3">
         <v>200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Z48" s="3">
         <v>200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AA48" s="3">
         <v>200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AB48" s="3">
         <v>300</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E49" s="3">
         <v>5900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G49" s="3">
         <v>6000</v>
-      </c>
-      <c r="F49" s="3">
-        <v>900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>900</v>
       </c>
       <c r="H49" s="3">
         <v>900</v>
@@ -3716,17 +4048,26 @@
       <c r="Y49" s="3">
         <v>900</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +4146,17 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,8 +4235,17 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3915,25 +4274,25 @@
         <v>600</v>
       </c>
       <c r="L52" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="M52" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="N52" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="O52" s="3">
         <v>900</v>
       </c>
       <c r="P52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="Q52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="R52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="S52" s="3">
         <v>1200</v>
@@ -3942,31 +4301,40 @@
         <v>1200</v>
       </c>
       <c r="U52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="W52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X52" s="3">
         <v>600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="Y52" s="3">
         <v>600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Z52" s="3">
         <v>600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="AA52" s="3">
         <v>300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AB52" s="3">
         <v>300</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4413,106 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>28800</v>
+      </c>
+      <c r="F54" s="3">
         <v>29400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>31100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>26000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>25300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>24900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
+        <v>24900</v>
+      </c>
+      <c r="L54" s="3">
         <v>22200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>23000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>22500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>22100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>21000</v>
-      </c>
-      <c r="N54" s="3">
-        <v>21100</v>
-      </c>
-      <c r="O54" s="3">
-        <v>21500</v>
-      </c>
-      <c r="P54" s="3">
-        <v>20800</v>
       </c>
       <c r="Q54" s="3">
         <v>21100</v>
       </c>
       <c r="R54" s="3">
+        <v>21500</v>
+      </c>
+      <c r="S54" s="3">
+        <v>20800</v>
+      </c>
+      <c r="T54" s="3">
+        <v>21100</v>
+      </c>
+      <c r="U54" s="3">
         <v>19700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="V54" s="3">
         <v>19300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="W54" s="3">
         <v>18800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="X54" s="3">
         <v>17700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Y54" s="3">
         <v>16400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Z54" s="3">
         <v>16000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AA54" s="3">
         <v>16700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AB54" s="3">
         <v>16900</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4541,11 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,99 +4574,111 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F57" s="3">
         <v>700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
+        <v>900</v>
+      </c>
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>1800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="S57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="T57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="V57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="W57" s="3">
         <v>900</v>
-      </c>
-      <c r="U57" s="3">
-        <v>700</v>
-      </c>
-      <c r="V57" s="3">
-        <v>500</v>
-      </c>
-      <c r="W57" s="3">
-        <v>700</v>
       </c>
       <c r="X57" s="3">
         <v>700</v>
       </c>
       <c r="Y57" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z57" s="3">
         <v>700</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB57" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
         <v>0</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>8</v>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>8</v>
@@ -4291,21 +4692,21 @@
       <c r="J58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N58" s="3">
         <v>700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>700</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
@@ -4315,14 +4716,14 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -4345,168 +4746,195 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F59" s="3">
         <v>3900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>4000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L59" s="3">
         <v>1600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>1800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="M59" s="3">
-        <v>2100</v>
       </c>
       <c r="N59" s="3">
         <v>1800</v>
       </c>
       <c r="O59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="R59" s="3">
         <v>1900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="S59" s="3">
         <v>1500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="T59" s="3">
         <v>1500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="U59" s="3">
         <v>1400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="V59" s="3">
         <v>1200</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="U59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V59" s="3">
-        <v>1100</v>
       </c>
       <c r="W59" s="3">
         <v>1100</v>
       </c>
       <c r="X59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y59" s="3">
         <v>1100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AB59" s="3">
         <v>1300</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F60" s="3">
         <v>4700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L60" s="3">
         <v>2600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>4000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>4300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>3500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="Q60" s="3">
         <v>3200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="R60" s="3">
         <v>2900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="S60" s="3">
         <v>2600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="T60" s="3">
         <v>3400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="U60" s="3">
         <v>2700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="V60" s="3">
         <v>2400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="W60" s="3">
         <v>2100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="X60" s="3">
         <v>1700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Y60" s="3">
         <v>1600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Z60" s="3">
         <v>1800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="AA60" s="3">
         <v>1800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AB60" s="3">
         <v>2000</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4529,23 +4957,23 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>1600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>900</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -4559,20 +4987,20 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="X61" s="3">
         <v>500</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4585,76 +5013,85 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E62" s="3">
         <v>4500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
+        <v>4500</v>
+      </c>
+      <c r="G62" s="3">
         <v>5300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="Q62" s="3">
         <v>800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="R62" s="3">
         <v>1100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="S62" s="3">
         <v>800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="T62" s="3">
         <v>900</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
-      </c>
-      <c r="X62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -4665,8 +5102,17 @@
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +5191,17 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +5280,17 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5369,106 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F66" s="3">
         <v>9200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>10400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
+        <v>5400</v>
+      </c>
+      <c r="L66" s="3">
         <v>3000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>5600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>5300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>5800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>4200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="Q66" s="3">
         <v>4000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="R66" s="3">
         <v>4000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="S66" s="3">
         <v>3400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="T66" s="3">
         <v>4200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="U66" s="3">
         <v>2700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="V66" s="3">
         <v>2400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="W66" s="3">
         <v>2600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="X66" s="3">
         <v>2200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Y66" s="3">
         <v>1600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Z66" s="3">
         <v>1800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AA66" s="3">
         <v>1800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AB66" s="3">
         <v>2000</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5497,11 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5580,17 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5669,17 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5758,17 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5847,106 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3200</v>
+        <v>3500</v>
       </c>
       <c r="E72" s="3">
-        <v>3600</v>
+        <v>2800</v>
       </c>
       <c r="F72" s="3">
         <v>3200</v>
       </c>
       <c r="G72" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H72" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I72" s="3">
         <v>3000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L72" s="3">
         <v>1800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>-100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>-200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>-1100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>-700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="Q72" s="3">
         <v>-500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="R72" s="3">
         <v>-300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="S72" s="3">
         <v>-300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="T72" s="3">
         <v>-800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="U72" s="3">
         <v>-700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="V72" s="3">
         <v>-1200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="W72" s="3">
         <v>-1700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="X72" s="3">
         <v>-2500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Y72" s="3">
         <v>-3200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Z72" s="3">
         <v>-3800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AA72" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AB72" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +6025,17 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +6114,17 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +6203,106 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F76" s="3">
         <v>20200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>20700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>20300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>20100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>19500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
+        <v>19500</v>
+      </c>
+      <c r="L76" s="3">
         <v>19200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>17400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>17200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>16400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>16800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>17100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>17500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="S76" s="3">
         <v>17500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="T76" s="3">
         <v>16900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="U76" s="3">
         <v>17000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="V76" s="3">
         <v>16800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="W76" s="3">
         <v>16300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="X76" s="3">
         <v>15500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Y76" s="3">
         <v>14700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Z76" s="3">
         <v>14200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AA76" s="3">
         <v>14900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AB76" s="3">
         <v>14800</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6381,200 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="E80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44469</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>44104</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="T80" s="2">
         <v>43555</v>
       </c>
-      <c r="R80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="V80" s="2">
         <v>43373</v>
       </c>
-      <c r="T80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2">
+      <c r="X80" s="2">
         <v>43190</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Z80" s="2">
         <v>43008</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AA80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AB80" s="2">
         <v>42825</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AC80" s="2">
         <v>42735</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AD80" s="2">
         <v>42643</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AE80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>700</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G81" s="3">
         <v>-400</v>
-      </c>
-      <c r="E81" s="3">
-        <v>500</v>
-      </c>
-      <c r="F81" s="3">
-        <v>200</v>
-      </c>
-      <c r="G81" s="3">
-        <v>700</v>
       </c>
       <c r="H81" s="3">
         <v>500</v>
       </c>
       <c r="I81" s="3">
+        <v>200</v>
+      </c>
+      <c r="J81" s="3">
+        <v>700</v>
+      </c>
+      <c r="K81" s="3">
+        <v>500</v>
+      </c>
+      <c r="L81" s="3">
         <v>1800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-200</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>100</v>
-      </c>
       <c r="R81" s="3">
-        <v>2200</v>
+        <v>0</v>
       </c>
       <c r="S81" s="3">
         <v>600</v>
       </c>
       <c r="T81" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="U81" s="3">
-        <v>400</v>
+        <v>2200</v>
       </c>
       <c r="V81" s="3">
-        <v>1800</v>
+        <v>600</v>
       </c>
       <c r="W81" s="3">
         <v>700</v>
       </c>
       <c r="X81" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>700</v>
+      </c>
+      <c r="AA81" s="3">
         <v>200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AB81" s="3">
         <v>300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AC81" s="3">
         <v>800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AD81" s="3">
         <v>500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AE81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,22 +6603,25 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>100</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H83" s="3">
         <v>0</v>
@@ -6033,14 +6629,14 @@
       <c r="I83" s="3">
         <v>0</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>8</v>
@@ -6051,26 +6647,26 @@
       <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3">
+        <v>0</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U83" s="3">
         <v>100</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -6090,8 +6686,17 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6775,17 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6864,17 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6953,17 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +7042,17 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,76 +7131,85 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-300</v>
+      <c r="D89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E89" s="3">
-        <v>300</v>
+        <v>1100</v>
       </c>
       <c r="F89" s="3">
+        <v>-800</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="I89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>1600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>1800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>-400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="S89" s="3">
         <v>900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="T89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="U89" s="3">
         <v>3700</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -6570,8 +7220,17 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,20 +7259,23 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>-100</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
@@ -6644,23 +7306,23 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -6680,8 +7342,17 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +7431,17 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,8 +7520,17 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6884,23 +7573,23 @@
       <c r="P94" s="3">
         <v>0</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U94" s="3">
         <v>100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -6920,8 +7609,17 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7648,11 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7030,8 +7731,17 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7820,17 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7909,17 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,8 +7998,17 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7314,23 +8051,23 @@
       <c r="P100" s="3">
         <v>0</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U100" s="3">
         <v>-300</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -7350,8 +8087,17 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7430,8 +8176,17 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7474,23 +8229,23 @@
       <c r="P102" s="3">
         <v>0</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
+      <c r="Q102" s="3">
+        <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U102" s="3">
         <v>3600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
@@ -7508,6 +8263,15 @@
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>ORBT</t>
   </si>
@@ -656,14 +656,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -683,376 +684,427 @@
     <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AI7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E8" s="3">
+        <v>6200</v>
+      </c>
+      <c r="F8" s="3">
+        <v>27600</v>
+      </c>
+      <c r="G8" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H8" s="3">
         <v>5200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="I8" s="3">
         <v>7500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="J8" s="3">
         <v>6000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H8" s="3">
-        <v>6800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J8" s="3">
-        <v>6100</v>
       </c>
       <c r="K8" s="3">
         <v>5800</v>
       </c>
       <c r="L8" s="3">
-        <v>5400</v>
+        <v>6800</v>
       </c>
       <c r="M8" s="3">
-        <v>6400</v>
+        <v>5000</v>
       </c>
       <c r="N8" s="3">
-        <v>7900</v>
+        <v>6100</v>
       </c>
       <c r="O8" s="3">
         <v>5800</v>
       </c>
       <c r="P8" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>6400</v>
+      </c>
+      <c r="R8" s="3">
+        <v>7900</v>
+      </c>
+      <c r="S8" s="3">
+        <v>5800</v>
+      </c>
+      <c r="T8" s="3">
         <v>5900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>6500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>6100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>6900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>6500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>24700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>6300</v>
-      </c>
-      <c r="W8" s="3">
-        <v>5000</v>
-      </c>
-      <c r="X8" s="3">
-        <v>5300</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>20900</v>
-      </c>
-      <c r="Z8" s="3">
-        <v>5000</v>
       </c>
       <c r="AA8" s="3">
         <v>5000</v>
       </c>
       <c r="AB8" s="3">
+        <v>5300</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>20900</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AF8" s="3">
         <v>5200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AG8" s="3">
         <v>5500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AH8" s="3">
         <v>5500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AI8" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F9" s="3">
+        <v>18800</v>
+      </c>
+      <c r="G9" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H9" s="3">
         <v>4100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="I9" s="3">
         <v>4700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="J9" s="3">
         <v>4100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="K9" s="3">
         <v>4200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="L9" s="3">
         <v>4300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="M9" s="3">
         <v>3000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="N9" s="3">
         <v>3800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="O9" s="3">
         <v>3600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="P9" s="3">
         <v>3700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="Q9" s="3">
         <v>4700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="R9" s="3">
         <v>5400</v>
-      </c>
-      <c r="O9" s="3">
-        <v>4700</v>
-      </c>
-      <c r="P9" s="3">
-        <v>4100</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>4900</v>
-      </c>
-      <c r="R9" s="3">
-        <v>4300</v>
       </c>
       <c r="S9" s="3">
         <v>4700</v>
       </c>
       <c r="T9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="U9" s="3">
+        <v>4900</v>
+      </c>
+      <c r="V9" s="3">
+        <v>4300</v>
+      </c>
+      <c r="W9" s="3">
+        <v>4700</v>
+      </c>
+      <c r="X9" s="3">
         <v>4800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>16500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>4100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>3300</v>
-      </c>
-      <c r="X9" s="3">
-        <v>3200</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>12700</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>2900</v>
-      </c>
-      <c r="AA9" s="3">
-        <v>3200</v>
       </c>
       <c r="AB9" s="3">
         <v>3200</v>
       </c>
       <c r="AC9" s="3">
+        <v>12700</v>
+      </c>
+      <c r="AD9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AE9" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AG9" s="3">
         <v>3300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AH9" s="3">
         <v>3500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AI9" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>8800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H10" s="3">
         <v>1100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="I10" s="3">
         <v>2800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="J10" s="3">
         <v>1900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="K10" s="3">
         <v>1600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="L10" s="3">
         <v>2500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="M10" s="3">
         <v>2000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="N10" s="3">
         <v>2300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="O10" s="3">
         <v>2200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="P10" s="3">
         <v>1700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>1700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>2500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>1100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>1800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>1600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>1800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>2200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>1700</v>
-      </c>
-      <c r="U10" s="3">
-        <v>8200</v>
-      </c>
-      <c r="V10" s="3">
-        <v>2200</v>
-      </c>
-      <c r="W10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="X10" s="3">
-        <v>2100</v>
       </c>
       <c r="Y10" s="3">
         <v>8200</v>
       </c>
       <c r="Z10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB10" s="3">
         <v>2100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
+        <v>8200</v>
+      </c>
+      <c r="AD10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AE10" s="3">
         <v>1800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AF10" s="3">
         <v>2000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AG10" s="3">
         <v>2200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AH10" s="3">
         <v>2000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AI10" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1136,12 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1229,20 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,97 +1330,121 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-1600</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,8 +1532,20 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,79 +1574,83 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>6400</v>
+        <v>7200</v>
       </c>
       <c r="E17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="F17" s="3">
+        <v>28500</v>
+      </c>
+      <c r="G17" s="3">
         <v>7100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>6300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>6300</v>
       </c>
       <c r="H17" s="3">
         <v>6400</v>
       </c>
       <c r="I17" s="3">
+        <v>7100</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L17" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M17" s="3">
         <v>4800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="N17" s="3">
         <v>5400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="O17" s="3">
         <v>5200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>3500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>6200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="R17" s="3">
         <v>7000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>6100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>5800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>6700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>6100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>6300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>6400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>23000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>5700</v>
-      </c>
-      <c r="W17" s="3">
-        <v>4800</v>
-      </c>
-      <c r="X17" s="3">
-        <v>4900</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>19300</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>4600</v>
       </c>
       <c r="AA17" s="3">
         <v>4800</v>
@@ -1551,105 +1659,129 @@
         <v>4900</v>
       </c>
       <c r="AC17" s="3">
+        <v>19300</v>
+      </c>
+      <c r="AD17" s="3">
+        <v>4600</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AF17" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AG17" s="3">
         <v>5000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <v>5100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AI17" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H18" s="3">
         <v>-1200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="I18" s="3">
         <v>400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="J18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="K18" s="3">
         <v>-500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="L18" s="3">
         <v>400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>700</v>
-      </c>
-      <c r="K18" s="3">
-        <v>600</v>
-      </c>
-      <c r="L18" s="3">
-        <v>1900</v>
       </c>
       <c r="M18" s="3">
         <v>200</v>
       </c>
       <c r="N18" s="3">
+        <v>700</v>
+      </c>
+      <c r="O18" s="3">
+        <v>600</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>200</v>
+      </c>
+      <c r="R18" s="3">
         <v>900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>-300</v>
-      </c>
-      <c r="P18" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="R18" s="3">
-        <v>0</v>
-      </c>
-      <c r="S18" s="3">
-        <v>600</v>
       </c>
       <c r="T18" s="3">
         <v>100</v>
       </c>
       <c r="U18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V18" s="3">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3">
+        <v>600</v>
+      </c>
+      <c r="X18" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y18" s="3">
         <v>1700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>600</v>
-      </c>
-      <c r="W18" s="3">
-        <v>200</v>
-      </c>
-      <c r="X18" s="3">
-        <v>400</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>400</v>
       </c>
       <c r="AA18" s="3">
         <v>200</v>
       </c>
       <c r="AB18" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AC18" s="3">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="AD18" s="3">
         <v>400</v>
       </c>
       <c r="AE18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF18" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG18" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH18" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,62 +1813,66 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="H20" s="3">
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -1750,97 +1886,109 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="J21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="K21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="L21" s="3">
         <v>500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>200</v>
-      </c>
-      <c r="J21" s="3">
-        <v>700</v>
-      </c>
-      <c r="K21" s="3">
-        <v>600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>1900</v>
       </c>
       <c r="M21" s="3">
         <v>200</v>
       </c>
       <c r="N21" s="3">
+        <v>700</v>
+      </c>
+      <c r="O21" s="3">
+        <v>600</v>
+      </c>
+      <c r="P21" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>200</v>
+      </c>
+      <c r="R21" s="3">
         <v>900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="S21" s="3">
         <v>-400</v>
-      </c>
-      <c r="P21" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R21" s="3">
-        <v>0</v>
-      </c>
-      <c r="S21" s="3">
-        <v>600</v>
       </c>
       <c r="T21" s="3">
         <v>100</v>
       </c>
       <c r="U21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V21" s="3">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
+        <v>600</v>
+      </c>
+      <c r="X21" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y21" s="3">
         <v>1800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1859,25 +2007,37 @@
       <c r="AE21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1885,8 +2045,8 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
@@ -1936,8 +2096,8 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -1948,97 +2108,121 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="E23" s="3">
-        <v>700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-300</v>
       </c>
       <c r="G23" s="3">
         <v>-400</v>
       </c>
       <c r="H23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I23" s="3">
+        <v>700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L23" s="3">
         <v>500</v>
-      </c>
-      <c r="I23" s="3">
-        <v>200</v>
-      </c>
-      <c r="J23" s="3">
-        <v>700</v>
-      </c>
-      <c r="K23" s="3">
-        <v>600</v>
-      </c>
-      <c r="L23" s="3">
-        <v>1800</v>
       </c>
       <c r="M23" s="3">
         <v>200</v>
       </c>
       <c r="N23" s="3">
+        <v>700</v>
+      </c>
+      <c r="O23" s="3">
+        <v>600</v>
+      </c>
+      <c r="P23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>200</v>
+      </c>
+      <c r="R23" s="3">
         <v>800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="S23" s="3">
         <v>-400</v>
       </c>
-      <c r="P23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <v>100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Y23" s="3">
         <v>1700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>600</v>
-      </c>
-      <c r="W23" s="3">
-        <v>200</v>
-      </c>
-      <c r="X23" s="3">
-        <v>400</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>1600</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>400</v>
       </c>
       <c r="AA23" s="3">
         <v>200</v>
       </c>
       <c r="AB23" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AC23" s="3">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="AD23" s="3">
         <v>400</v>
       </c>
       <c r="AE23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="AF23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG23" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2049,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -2094,40 +2278,52 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-500</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-600</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AD24" s="3">
         <v>-300</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-300</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2411,222 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I26" s="3">
         <v>700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="L26" s="3">
         <v>500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>200</v>
-      </c>
-      <c r="J26" s="3">
-        <v>700</v>
-      </c>
-      <c r="K26" s="3">
-        <v>500</v>
-      </c>
-      <c r="L26" s="3">
-        <v>1800</v>
       </c>
       <c r="M26" s="3">
         <v>200</v>
       </c>
       <c r="N26" s="3">
+        <v>700</v>
+      </c>
+      <c r="O26" s="3">
+        <v>500</v>
+      </c>
+      <c r="P26" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>200</v>
+      </c>
+      <c r="R26" s="3">
         <v>900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="X26" s="3">
         <v>100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="Y26" s="3">
         <v>2200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z26" s="3">
         <v>600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA26" s="3">
         <v>700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AB26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AC26" s="3">
         <v>1800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AD26" s="3">
         <v>700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AE26" s="3">
         <v>200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AF26" s="3">
         <v>300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AG26" s="3">
         <v>800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AH26" s="3">
         <v>500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AI26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I27" s="3">
         <v>700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="L27" s="3">
         <v>500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>700</v>
-      </c>
-      <c r="K27" s="3">
-        <v>500</v>
-      </c>
-      <c r="L27" s="3">
-        <v>1800</v>
       </c>
       <c r="M27" s="3">
         <v>200</v>
       </c>
       <c r="N27" s="3">
+        <v>700</v>
+      </c>
+      <c r="O27" s="3">
+        <v>500</v>
+      </c>
+      <c r="P27" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>200</v>
+      </c>
+      <c r="R27" s="3">
         <v>900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>2200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AB27" s="3">
         <v>400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AC27" s="3">
         <v>1800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AD27" s="3">
         <v>700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AE27" s="3">
         <v>200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AF27" s="3">
         <v>300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AG27" s="3">
         <v>800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AH27" s="3">
         <v>500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AI27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2714,20 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2571,8 +2815,20 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2916,20 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,62 +3017,74 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="H32" s="3">
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -2818,117 +3098,141 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I33" s="3">
         <v>700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="L33" s="3">
         <v>500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>200</v>
-      </c>
-      <c r="J33" s="3">
-        <v>700</v>
-      </c>
-      <c r="K33" s="3">
-        <v>500</v>
-      </c>
-      <c r="L33" s="3">
-        <v>1800</v>
       </c>
       <c r="M33" s="3">
         <v>200</v>
       </c>
       <c r="N33" s="3">
+        <v>700</v>
+      </c>
+      <c r="O33" s="3">
+        <v>500</v>
+      </c>
+      <c r="P33" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>200</v>
+      </c>
+      <c r="R33" s="3">
         <v>900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>2200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AB33" s="3">
         <v>400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AC33" s="3">
         <v>1800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AD33" s="3">
         <v>700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AE33" s="3">
         <v>200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AF33" s="3">
         <v>300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AG33" s="3">
         <v>800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AH33" s="3">
         <v>500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AI33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3320,227 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I35" s="3">
         <v>700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="L35" s="3">
         <v>500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>200</v>
-      </c>
-      <c r="J35" s="3">
-        <v>700</v>
-      </c>
-      <c r="K35" s="3">
-        <v>500</v>
-      </c>
-      <c r="L35" s="3">
-        <v>1800</v>
       </c>
       <c r="M35" s="3">
         <v>200</v>
       </c>
       <c r="N35" s="3">
+        <v>700</v>
+      </c>
+      <c r="O35" s="3">
+        <v>500</v>
+      </c>
+      <c r="P35" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>200</v>
+      </c>
+      <c r="R35" s="3">
         <v>900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="X35" s="3">
         <v>100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Y35" s="3">
         <v>2200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Z35" s="3">
         <v>600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="AA35" s="3">
         <v>700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AB35" s="3">
         <v>400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AC35" s="3">
         <v>1800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AD35" s="3">
         <v>700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AE35" s="3">
         <v>200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AF35" s="3">
         <v>300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AG35" s="3">
         <v>800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AH35" s="3">
         <v>500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AI35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AI38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3572,12 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3609,113 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F41" s="3">
         <v>4200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>5300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L41" s="3">
+        <v>9200</v>
+      </c>
+      <c r="M41" s="3">
         <v>8300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>6900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>6900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>7000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>7500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>5700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>4400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="T41" s="3">
         <v>2800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="U41" s="3">
         <v>3600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="V41" s="3">
         <v>3900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="W41" s="3">
         <v>3600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>2900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Y41" s="3">
         <v>4500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>1600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AA41" s="3">
         <v>1100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AB41" s="3">
         <v>900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AC41" s="3">
         <v>900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AD41" s="3">
         <v>800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AE41" s="3">
         <v>2400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AF41" s="3">
         <v>1900</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE41" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI41" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3423,28 +3783,40 @@
         <v>0</v>
       </c>
       <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
         <v>300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AD42" s="3">
         <v>300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AE42" s="3">
         <v>200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AF42" s="3">
         <v>200</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE42" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3452,46 +3824,46 @@
         <v>4300</v>
       </c>
       <c r="E43" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F43" s="3">
+        <v>4300</v>
+      </c>
+      <c r="G43" s="3">
         <v>4000</v>
-      </c>
-      <c r="F43" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G43" s="3">
-        <v>3600</v>
       </c>
       <c r="H43" s="3">
         <v>3100</v>
       </c>
       <c r="I43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M43" s="3">
         <v>3300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>3700</v>
-      </c>
-      <c r="K43" s="3">
-        <v>3700</v>
-      </c>
-      <c r="L43" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M43" s="3">
-        <v>3400</v>
-      </c>
-      <c r="N43" s="3">
-        <v>4000</v>
       </c>
       <c r="O43" s="3">
         <v>3700</v>
       </c>
       <c r="P43" s="3">
-        <v>3800</v>
+        <v>3300</v>
       </c>
       <c r="Q43" s="3">
-        <v>3800</v>
+        <v>3400</v>
       </c>
       <c r="R43" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="S43" s="3">
         <v>3700</v>
@@ -3500,167 +3872,191 @@
         <v>3800</v>
       </c>
       <c r="U43" s="3">
-        <v>2400</v>
+        <v>3800</v>
       </c>
       <c r="V43" s="3">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="W43" s="3">
         <v>3700</v>
       </c>
       <c r="X43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Z43" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB43" s="3">
         <v>4300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AC43" s="3">
         <v>3300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AD43" s="3">
         <v>3000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AE43" s="3">
         <v>2700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AF43" s="3">
         <v>3000</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F44" s="3">
         <v>9600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>10600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>11100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>11800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>8500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
+        <v>11800</v>
+      </c>
+      <c r="L44" s="3">
+        <v>8500</v>
+      </c>
+      <c r="M44" s="3">
         <v>8400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>9000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>9000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>9400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>9400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="R44" s="3">
         <v>10000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="S44" s="3">
         <v>10800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="T44" s="3">
         <v>11200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="U44" s="3">
         <v>10500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="V44" s="3">
         <v>10300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="W44" s="3">
         <v>10000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="X44" s="3">
         <v>10700</v>
-      </c>
-      <c r="U44" s="3">
-        <v>10100</v>
-      </c>
-      <c r="V44" s="3">
-        <v>11400</v>
-      </c>
-      <c r="W44" s="3">
-        <v>10900</v>
-      </c>
-      <c r="X44" s="3">
-        <v>9600</v>
       </c>
       <c r="Y44" s="3">
         <v>10100</v>
       </c>
       <c r="Z44" s="3">
+        <v>11400</v>
+      </c>
+      <c r="AA44" s="3">
+        <v>10900</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>9600</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>10100</v>
+      </c>
+      <c r="AD44" s="3">
         <v>10000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AE44" s="3">
         <v>10000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AF44" s="3">
         <v>10000</v>
       </c>
-      <c r="AC44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE44" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI44" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>400</v>
+      </c>
+      <c r="E45" s="3">
+        <v>600</v>
+      </c>
+      <c r="F45" s="3">
         <v>700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>400</v>
       </c>
       <c r="I45" s="3">
         <v>400</v>
       </c>
       <c r="J45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L45" s="3">
         <v>400</v>
       </c>
       <c r="M45" s="3">
+        <v>400</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
-        <v>400</v>
-      </c>
       <c r="O45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P45" s="3">
         <v>400</v>
@@ -3669,138 +4065,162 @@
         <v>300</v>
       </c>
       <c r="R45" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S45" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="T45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="U45" s="3">
         <v>300</v>
       </c>
       <c r="V45" s="3">
+        <v>500</v>
+      </c>
+      <c r="W45" s="3">
+        <v>200</v>
+      </c>
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA45" s="3">
         <v>900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="AB45" s="3">
         <v>1200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AD45" s="3">
         <v>200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AF45" s="3">
         <v>300</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>15700</v>
+      </c>
+      <c r="F46" s="3">
         <v>18700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>19000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>19400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>21100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>21300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
+        <v>21100</v>
+      </c>
+      <c r="L46" s="3">
+        <v>21300</v>
+      </c>
+      <c r="M46" s="3">
         <v>20400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>19800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>19800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>20100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>20600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>20100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>19300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="T46" s="3">
         <v>18200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="U46" s="3">
         <v>18200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="V46" s="3">
         <v>18500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="W46" s="3">
         <v>17400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="X46" s="3">
         <v>17600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="Y46" s="3">
         <v>17400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="3">
         <v>16900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="AA46" s="3">
         <v>16500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="AB46" s="3">
         <v>15900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AC46" s="3">
         <v>14700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AD46" s="3">
         <v>14400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AE46" s="3">
         <v>15300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AF46" s="3">
         <v>15400</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE46" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI46" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3888,123 +4308,147 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F48" s="3">
         <v>3400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H48" s="3">
-        <v>3300</v>
       </c>
       <c r="I48" s="3">
         <v>3400</v>
       </c>
       <c r="J48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M48" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N48" s="3">
         <v>3600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>3600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>1000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>1100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="T48" s="3">
         <v>1100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="U48" s="3">
         <v>1200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="V48" s="3">
         <v>1300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="W48" s="3">
         <v>1400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="X48" s="3">
         <v>1500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Y48" s="3">
         <v>300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="AA48" s="3">
         <v>300</v>
-      </c>
-      <c r="X48" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>200</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>200</v>
       </c>
       <c r="AB48" s="3">
         <v>300</v>
       </c>
-      <c r="AC48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE48" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="F49" s="3">
         <v>6300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>5900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>5900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>6000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>900</v>
-      </c>
-      <c r="I49" s="3">
-        <v>900</v>
       </c>
       <c r="J49" s="3">
         <v>900</v>
       </c>
       <c r="K49" s="3">
-        <v>900</v>
+        <v>6000</v>
       </c>
       <c r="L49" s="3">
         <v>900</v>
@@ -4057,17 +4501,29 @@
       <c r="AB49" s="3">
         <v>900</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4611,20 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4712,20 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4283,58 +4763,70 @@
         <v>600</v>
       </c>
       <c r="O52" s="3">
+        <v>600</v>
+      </c>
+      <c r="P52" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>600</v>
+      </c>
+      <c r="R52" s="3">
+        <v>600</v>
+      </c>
+      <c r="S52" s="3">
         <v>900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="T52" s="3">
         <v>900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="U52" s="3">
         <v>900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="V52" s="3">
         <v>900</v>
-      </c>
-      <c r="S52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="V52" s="3">
-        <v>1200</v>
       </c>
       <c r="W52" s="3">
         <v>1200</v>
       </c>
       <c r="X52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB52" s="3">
         <v>600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AC52" s="3">
         <v>600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AD52" s="3">
         <v>600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AE52" s="3">
         <v>300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AF52" s="3">
         <v>300</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE52" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI52" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4914,121 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E54" s="3">
+        <v>26200</v>
+      </c>
+      <c r="F54" s="3">
         <v>29100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>28800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>29400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>31100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>26000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
+        <v>31100</v>
+      </c>
+      <c r="L54" s="3">
+        <v>26000</v>
+      </c>
+      <c r="M54" s="3">
         <v>25300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>24900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>24900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>22200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>23000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>22500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>22100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="T54" s="3">
         <v>21000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="U54" s="3">
         <v>21100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="V54" s="3">
         <v>21500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="W54" s="3">
         <v>20800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="X54" s="3">
         <v>21100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Y54" s="3">
         <v>19700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>19300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AA54" s="3">
         <v>18800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AB54" s="3">
         <v>17700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AC54" s="3">
         <v>16400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AD54" s="3">
         <v>16000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AE54" s="3">
         <v>16700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AF54" s="3">
         <v>16900</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE54" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI54" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +5060,12 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,114 +5097,130 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>900</v>
+      </c>
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L57" s="3">
+        <v>500</v>
+      </c>
+      <c r="M57" s="3">
         <v>800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="T57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="U57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="V57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="W57" s="3">
         <v>1100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="X57" s="3">
         <v>1900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="Y57" s="3">
         <v>1300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>1300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="AA57" s="3">
         <v>900</v>
-      </c>
-      <c r="X57" s="3">
-        <v>700</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>500</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>700</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>700</v>
       </c>
       <c r="AB57" s="3">
         <v>700</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE57" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD57" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE57" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF57" s="3">
+        <v>700</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI57" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>8</v>
@@ -4701,41 +5237,41 @@
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3">
         <v>700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="S58" s="3">
         <v>700</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4755,194 +5291,230 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3800</v>
+        <v>4100</v>
       </c>
       <c r="E59" s="3">
         <v>3800</v>
       </c>
       <c r="F59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H59" s="3">
         <v>3900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>4000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>1500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>1600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P59" s="3">
-        <v>2100</v>
       </c>
       <c r="Q59" s="3">
         <v>1800</v>
       </c>
       <c r="R59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="S59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="U59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V59" s="3">
         <v>1900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="W59" s="3">
         <v>1500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="X59" s="3">
         <v>1500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="Y59" s="3">
         <v>1400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>1200</v>
-      </c>
-      <c r="W59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>1100</v>
       </c>
       <c r="AA59" s="3">
         <v>1100</v>
       </c>
       <c r="AB59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AD59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AE59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF59" s="3">
         <v>1300</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>4900</v>
+        <v>6100</v>
       </c>
       <c r="E60" s="3">
         <v>4800</v>
       </c>
       <c r="F60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H60" s="3">
         <v>4700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L60" s="3">
+        <v>3000</v>
+      </c>
+      <c r="M60" s="3">
         <v>2200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>2400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>2400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>2600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>3600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>4000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="S60" s="3">
         <v>4300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="T60" s="3">
         <v>3500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="U60" s="3">
         <v>3200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="V60" s="3">
         <v>2900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="W60" s="3">
         <v>2600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="X60" s="3">
         <v>3400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="Y60" s="3">
         <v>2700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Z60" s="3">
         <v>2400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="AA60" s="3">
         <v>2100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="AB60" s="3">
         <v>1700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AC60" s="3">
         <v>1600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AD60" s="3">
         <v>1800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AE60" s="3">
         <v>1800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AF60" s="3">
         <v>2000</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE60" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI60" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
@@ -4966,26 +5538,26 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>1600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="R61" s="3">
         <v>900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="S61" s="3">
         <v>900</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4996,23 +5568,23 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="AB61" s="3">
         <v>500</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
       <c r="AC61" s="3">
         <v>0</v>
       </c>
@@ -5022,88 +5594,100 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F62" s="3">
         <v>4200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>5300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>2800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="L62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M62" s="3">
         <v>3100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>3000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>3000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="R62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="S62" s="3">
         <v>600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="T62" s="3">
         <v>700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="U62" s="3">
         <v>800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="V62" s="3">
         <v>1100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="W62" s="3">
         <v>800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="X62" s="3">
         <v>900</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD62" s="3">
         <v>0</v>
@@ -5111,8 +5695,20 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5796,20 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5897,20 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5998,121 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F66" s="3">
         <v>9000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>9300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>9200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>10400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
+        <v>10400</v>
+      </c>
+      <c r="L66" s="3">
+        <v>5800</v>
+      </c>
+      <c r="M66" s="3">
         <v>5200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>5400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>5400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>3000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>5600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>5300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>5800</v>
-      </c>
-      <c r="P66" s="3">
-        <v>4200</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>4000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>4000</v>
-      </c>
-      <c r="S66" s="3">
-        <v>3400</v>
       </c>
       <c r="T66" s="3">
         <v>4200</v>
       </c>
       <c r="U66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W66" s="3">
+        <v>3400</v>
+      </c>
+      <c r="X66" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Y66" s="3">
         <v>2700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>2400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AA66" s="3">
         <v>2600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AB66" s="3">
         <v>2200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AC66" s="3">
         <v>1600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AD66" s="3">
         <v>1800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AE66" s="3">
         <v>1800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AF66" s="3">
         <v>2000</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE66" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI66" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +6144,12 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +6237,20 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +6338,20 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +6439,20 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6540,121 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F72" s="3">
         <v>3500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2800</v>
-      </c>
-      <c r="F72" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G72" s="3">
-        <v>3600</v>
       </c>
       <c r="H72" s="3">
         <v>3200</v>
       </c>
       <c r="I72" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J72" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K72" s="3">
+        <v>3600</v>
+      </c>
+      <c r="L72" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M72" s="3">
         <v>3000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>2300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>2300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>1800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>-100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>-200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>-1100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="T72" s="3">
         <v>-700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="U72" s="3">
         <v>-500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="V72" s="3">
         <v>-300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="W72" s="3">
         <v>-300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="X72" s="3">
         <v>-800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>-700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>-1200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="AA72" s="3">
         <v>-1700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AB72" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AC72" s="3">
         <v>-3200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AD72" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AE72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AF72" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE72" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6742,20 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6843,20 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6944,121 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>17700</v>
+      </c>
+      <c r="F76" s="3">
         <v>20000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>19500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>20200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>20700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>20300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
+        <v>20700</v>
+      </c>
+      <c r="L76" s="3">
+        <v>20300</v>
+      </c>
+      <c r="M76" s="3">
         <v>20100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>19500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>19500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>19200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>17400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>17200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>16400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="T76" s="3">
         <v>16800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>17100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>17500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>17500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>16900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>17000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>16800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AA76" s="3">
         <v>16300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AB76" s="3">
         <v>15500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AC76" s="3">
         <v>14700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AD76" s="3">
         <v>14200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AE76" s="3">
         <v>14900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AF76" s="3">
         <v>14800</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE76" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI76" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +7146,227 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="W80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AI80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I81" s="3">
         <v>700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="L81" s="3">
         <v>500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>200</v>
-      </c>
-      <c r="J81" s="3">
-        <v>700</v>
-      </c>
-      <c r="K81" s="3">
-        <v>500</v>
-      </c>
-      <c r="L81" s="3">
-        <v>1800</v>
       </c>
       <c r="M81" s="3">
         <v>200</v>
       </c>
       <c r="N81" s="3">
+        <v>700</v>
+      </c>
+      <c r="O81" s="3">
+        <v>500</v>
+      </c>
+      <c r="P81" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q81" s="3">
+        <v>200</v>
+      </c>
+      <c r="R81" s="3">
         <v>900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>2200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AA81" s="3">
         <v>700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AB81" s="3">
         <v>400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AC81" s="3">
         <v>1800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AD81" s="3">
         <v>700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AE81" s="3">
         <v>200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AF81" s="3">
         <v>300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AG81" s="3">
         <v>800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AH81" s="3">
         <v>500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AI81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,49 +7398,53 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>200</v>
       </c>
       <c r="E83" s="3">
+        <v>200</v>
+      </c>
+      <c r="F83" s="3">
+        <v>500</v>
+      </c>
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>8</v>
@@ -6656,29 +7452,29 @@
       <c r="R83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y83" s="3">
         <v>100</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -6695,8 +7491,20 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +7592,20 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7693,20 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7794,20 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7895,20 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,88 +7996,100 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>-1500</v>
       </c>
       <c r="E89" s="3">
+        <v>700</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I89" s="3">
         <v>1100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>-800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="R89" s="3">
         <v>1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="S89" s="3">
         <v>200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="U89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="V89" s="3">
         <v>400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="W89" s="3">
         <v>900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="X89" s="3">
         <v>-1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="Y89" s="3">
         <v>3700</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>0</v>
+      <c r="Z89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD89" s="3">
         <v>0</v>
@@ -7229,8 +8097,20 @@
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,79 +8142,83 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -7351,8 +8235,20 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +8336,20 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,8 +8437,20 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7541,19 +8461,19 @@
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="G94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>-200</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -7582,26 +8502,26 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y94" s="3">
         <v>100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -7618,8 +8538,20 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +8583,12 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7663,10 +8599,10 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -7740,8 +8676,20 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8777,20 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8878,20 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,31 +8979,43 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F100" s="3">
-        <v>0</v>
+        <v>-900</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+        <v>-200</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -8060,26 +9044,26 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
+      <c r="T100" s="3">
+        <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-300</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -8096,8 +9080,20 @@
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,31 +9181,43 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>-1600</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+        <v>-1400</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -8238,26 +9246,26 @@
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>8</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y102" s="3">
         <v>3600</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3">
-        <v>0</v>
+      <c r="Z102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
@@ -8272,6 +9280,18 @@
         <v>0</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
   <si>
     <t>ORBT</t>
   </si>
@@ -656,455 +656,468 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
-        <v>45291</v>
-      </c>
       <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44926</v>
       </c>
       <c r="J7" s="2">
         <v>44834</v>
       </c>
       <c r="K7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E8" s="3">
         <v>6600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6200</v>
       </c>
-      <c r="F8" s="3">
-        <v>27600</v>
-      </c>
       <c r="G8" s="3">
+        <v>8200</v>
+      </c>
+      <c r="H8" s="3">
         <v>7000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5200</v>
-      </c>
-      <c r="I8" s="3">
-        <v>7500</v>
       </c>
       <c r="J8" s="3">
         <v>6000</v>
       </c>
       <c r="K8" s="3">
+        <v>6000</v>
+      </c>
+      <c r="L8" s="3">
         <v>5800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>6500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>24700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>20900</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>5000</v>
       </c>
       <c r="AE8" s="3">
         <v>5000</v>
       </c>
       <c r="AF8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AG8" s="3">
         <v>5200</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>5500</v>
       </c>
       <c r="AH8" s="3">
         <v>5500</v>
       </c>
       <c r="AI8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E9" s="3">
         <v>4700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4300</v>
       </c>
-      <c r="F9" s="3">
-        <v>18800</v>
-      </c>
       <c r="G9" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H9" s="3">
         <v>4700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4100</v>
-      </c>
-      <c r="I9" s="3">
-        <v>4700</v>
       </c>
       <c r="J9" s="3">
         <v>4100</v>
       </c>
       <c r="K9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="L9" s="3">
         <v>4200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>16500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2900</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>3200</v>
       </c>
       <c r="AF9" s="3">
         <v>3200</v>
       </c>
       <c r="AG9" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AH9" s="3">
         <v>3300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1900</v>
+        <v>3100</v>
       </c>
       <c r="E10" s="3">
         <v>1900</v>
       </c>
       <c r="F10" s="3">
-        <v>8800</v>
+        <v>1900</v>
       </c>
       <c r="G10" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H10" s="3">
         <v>2300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1100</v>
       </c>
-      <c r="I10" s="3">
-        <v>2800</v>
-      </c>
       <c r="J10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K10" s="3">
         <v>1900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2200</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1700</v>
       </c>
       <c r="Q10" s="3">
         <v>1700</v>
       </c>
       <c r="R10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="S10" s="3">
         <v>2500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>8200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>8200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1140,8 +1153,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1241,8 +1255,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1342,8 +1359,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1353,8 +1373,8 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1362,8 +1382,8 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
         <v>0</v>
@@ -1372,41 +1392,41 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>100</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1422,8 +1442,8 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1434,8 +1454,8 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
@@ -1443,28 +1463,31 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1544,8 +1567,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,28 +1604,29 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E17" s="3">
         <v>7200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6900</v>
       </c>
-      <c r="F17" s="3">
-        <v>28500</v>
-      </c>
       <c r="G17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="H17" s="3">
         <v>7100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>7100</v>
       </c>
       <c r="J17" s="3">
         <v>6300</v>
@@ -1608,180 +1635,186 @@
         <v>6300</v>
       </c>
       <c r="L17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M17" s="3">
         <v>6400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>23000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>19300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-700</v>
       </c>
-      <c r="F18" s="3">
-        <v>-900</v>
-      </c>
       <c r="G18" s="3">
+        <v>800</v>
+      </c>
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>400</v>
       </c>
       <c r="J18" s="3">
         <v>-300</v>
       </c>
       <c r="K18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L18" s="3">
         <v>-500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
-        <v>0</v>
-      </c>
       <c r="W18" s="3">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
         <v>600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1817,40 +1850,41 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>300</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1865,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>-100</v>
@@ -1874,7 +1908,7 @@
         <v>-100</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -1898,11 +1932,11 @@
         <v>0</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -1918,80 +1952,83 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E21" s="3">
-        <v>-600</v>
+        <v>0</v>
       </c>
       <c r="F21" s="3">
         <v>-600</v>
       </c>
       <c r="G21" s="3">
+        <v>900</v>
+      </c>
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1000</v>
       </c>
-      <c r="I21" s="3">
-        <v>800</v>
-      </c>
       <c r="J21" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="K21" s="3">
         <v>-200</v>
       </c>
       <c r="L21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M21" s="3">
         <v>500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-100</v>
       </c>
-      <c r="V21" s="3">
-        <v>0</v>
-      </c>
       <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3">
         <v>600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1800</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2019,8 +2056,11 @@
       <c r="AI21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2042,17 +2082,17 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2060,11 +2100,11 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2072,11 +2112,11 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -2084,11 +2124,11 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2096,11 +2136,11 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2120,120 +2160,126 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>800</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I23" s="3">
-        <v>700</v>
       </c>
       <c r="J23" s="3">
         <v>-300</v>
       </c>
       <c r="K23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L23" s="3">
         <v>-400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-400</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
       <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
         <v>-200</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
       </c>
       <c r="F24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -2290,40 +2336,43 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-500</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-600</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-300</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
         <v>0</v>
       </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-300</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2423,210 +2472,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
+        <v>800</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>700</v>
       </c>
       <c r="J26" s="3">
         <v>-300</v>
       </c>
       <c r="K26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L26" s="3">
         <v>-400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-400</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
       <c r="U26" s="3">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>800</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I27" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>700</v>
       </c>
       <c r="J27" s="3">
         <v>-300</v>
       </c>
       <c r="K27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L27" s="3">
         <v>-400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-400</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
       <c r="U27" s="3">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2726,8 +2784,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2827,8 +2888,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2928,8 +2992,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3029,40 +3096,43 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-300</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -3077,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>100</v>
@@ -3086,7 +3156,7 @@
         <v>100</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V32" s="3">
         <v>0</v>
@@ -3110,11 +3180,11 @@
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3130,109 +3200,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>800</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>700</v>
       </c>
       <c r="J33" s="3">
         <v>-300</v>
       </c>
       <c r="K33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L33" s="3">
         <v>-400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-400</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
       <c r="U33" s="3">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3332,215 +3408,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>800</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>700</v>
       </c>
       <c r="J35" s="3">
         <v>-300</v>
       </c>
       <c r="K35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L35" s="3">
         <v>-400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-400</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
       <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
-        <v>45291</v>
-      </c>
       <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44926</v>
       </c>
       <c r="J38" s="2">
         <v>44834</v>
       </c>
       <c r="K38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3576,8 +3661,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3613,109 +3699,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1800</v>
       </c>
-      <c r="F41" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" s="3">
         <v>3400</v>
       </c>
-      <c r="H41" s="3">
-        <v>4700</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
+        <v>9200</v>
+      </c>
+      <c r="L41" s="3">
         <v>5300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>9200</v>
       </c>
-      <c r="K41" s="3">
-        <v>5300</v>
-      </c>
-      <c r="L41" s="3">
-        <v>9200</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8300</v>
-      </c>
-      <c r="N41" s="3">
-        <v>6900</v>
       </c>
       <c r="O41" s="3">
         <v>6900</v>
       </c>
       <c r="P41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="Q41" s="3">
         <v>7000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1100</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>900</v>
       </c>
       <c r="AC41" s="3">
         <v>900</v>
       </c>
       <c r="AD41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE41" s="3">
         <v>800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1900</v>
       </c>
-      <c r="AG41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3795,19 +3885,19 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AD42" s="3">
         <v>300</v>
       </c>
       <c r="AE42" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AF42" s="3">
         <v>200</v>
       </c>
-      <c r="AG42" s="3" t="s">
-        <v>8</v>
+      <c r="AG42" s="3">
+        <v>200</v>
       </c>
       <c r="AH42" s="3" t="s">
         <v>8</v>
@@ -3815,61 +3905,64 @@
       <c r="AI42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E43" s="3">
         <v>4300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3200</v>
       </c>
-      <c r="F43" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="3">
         <v>4000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>3100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>3600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>3100</v>
       </c>
-      <c r="K43" s="3">
-        <v>3600</v>
-      </c>
-      <c r="L43" s="3">
-        <v>3100</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3300</v>
-      </c>
-      <c r="N43" s="3">
-        <v>3700</v>
       </c>
       <c r="O43" s="3">
         <v>3700</v>
       </c>
       <c r="P43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Q43" s="3">
         <v>3300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3700</v>
-      </c>
-      <c r="T43" s="3">
-        <v>3800</v>
       </c>
       <c r="U43" s="3">
         <v>3800</v>
@@ -3878,129 +3971,132 @@
         <v>3800</v>
       </c>
       <c r="W43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="X43" s="3">
         <v>3700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>4300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3000</v>
       </c>
-      <c r="AG43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E44" s="3">
         <v>10300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10100</v>
       </c>
-      <c r="F44" s="3">
-        <v>9600</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
         <v>10600</v>
       </c>
-      <c r="H44" s="3">
-        <v>11100</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
+        <v>8500</v>
+      </c>
+      <c r="L44" s="3">
         <v>11800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>8500</v>
       </c>
-      <c r="K44" s="3">
-        <v>11800</v>
-      </c>
-      <c r="L44" s="3">
-        <v>8500</v>
-      </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8400</v>
-      </c>
-      <c r="N44" s="3">
-        <v>9000</v>
       </c>
       <c r="O44" s="3">
         <v>9000</v>
       </c>
       <c r="P44" s="3">
-        <v>9400</v>
+        <v>9000</v>
       </c>
       <c r="Q44" s="3">
         <v>9400</v>
       </c>
       <c r="R44" s="3">
+        <v>9400</v>
+      </c>
+      <c r="S44" s="3">
         <v>10000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>10800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>11200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>10500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>10300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>10000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>10700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>10100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>11400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>10900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>9600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>10100</v>
-      </c>
-      <c r="AD44" s="3">
-        <v>10000</v>
       </c>
       <c r="AE44" s="3">
         <v>10000</v>
@@ -4008,8 +4104,8 @@
       <c r="AF44" s="3">
         <v>10000</v>
       </c>
-      <c r="AG44" s="3" t="s">
-        <v>8</v>
+      <c r="AG44" s="3">
+        <v>10000</v>
       </c>
       <c r="AH44" s="3" t="s">
         <v>8</v>
@@ -4017,8 +4113,11 @@
       <c r="AI44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4026,22 +4125,22 @@
         <v>400</v>
       </c>
       <c r="E45" s="3">
+        <v>400</v>
+      </c>
+      <c r="F45" s="3">
         <v>600</v>
       </c>
-      <c r="F45" s="3">
-        <v>700</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>1000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>600</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>400</v>
       </c>
       <c r="K45" s="3">
         <v>400</v>
@@ -4053,19 +4152,19 @@
         <v>400</v>
       </c>
       <c r="N45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O45" s="3">
         <v>300</v>
       </c>
       <c r="P45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q45" s="3">
         <v>400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
-      </c>
-      <c r="R45" s="3">
-        <v>400</v>
       </c>
       <c r="S45" s="3">
         <v>400</v>
@@ -4074,16 +4173,16 @@
         <v>400</v>
       </c>
       <c r="U45" s="3">
+        <v>400</v>
+      </c>
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>200</v>
-      </c>
-      <c r="X45" s="3">
-        <v>300</v>
       </c>
       <c r="Y45" s="3">
         <v>300</v>
@@ -4092,158 +4191,164 @@
         <v>300</v>
       </c>
       <c r="AA45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB45" s="3">
         <v>900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>300</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E46" s="3">
         <v>15500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15700</v>
       </c>
-      <c r="F46" s="3">
-        <v>18700</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" s="3">
         <v>19000</v>
       </c>
-      <c r="H46" s="3">
-        <v>19400</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
+        <v>21300</v>
+      </c>
+      <c r="L46" s="3">
         <v>21100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>21300</v>
       </c>
-      <c r="K46" s="3">
-        <v>21100</v>
-      </c>
-      <c r="L46" s="3">
-        <v>21300</v>
-      </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20400</v>
-      </c>
-      <c r="N46" s="3">
-        <v>19800</v>
       </c>
       <c r="O46" s="3">
         <v>19800</v>
       </c>
       <c r="P46" s="3">
+        <v>19800</v>
+      </c>
+      <c r="Q46" s="3">
         <v>20100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>19300</v>
-      </c>
-      <c r="T46" s="3">
-        <v>18200</v>
       </c>
       <c r="U46" s="3">
         <v>18200</v>
       </c>
       <c r="V46" s="3">
+        <v>18200</v>
+      </c>
+      <c r="W46" s="3">
         <v>18500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15400</v>
       </c>
-      <c r="AG46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4320,76 +4425,79 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E48" s="3">
         <v>3600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3800</v>
       </c>
-      <c r="F48" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>3300</v>
-      </c>
-      <c r="H48" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I48" s="3">
-        <v>3400</v>
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J48" s="3">
         <v>3300</v>
       </c>
       <c r="K48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L48" s="3">
         <v>3400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3400</v>
-      </c>
-      <c r="N48" s="3">
-        <v>3600</v>
       </c>
       <c r="O48" s="3">
         <v>3600</v>
       </c>
       <c r="P48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q48" s="3">
         <v>700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1000</v>
-      </c>
-      <c r="S48" s="3">
-        <v>1100</v>
       </c>
       <c r="T48" s="3">
         <v>1100</v>
       </c>
       <c r="U48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V48" s="3">
         <v>1200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1500</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>300</v>
       </c>
       <c r="Z48" s="3">
         <v>300</v>
@@ -4401,7 +4509,7 @@
         <v>300</v>
       </c>
       <c r="AC48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD48" s="3">
         <v>200</v>
@@ -4410,48 +4518,51 @@
         <v>200</v>
       </c>
       <c r="AF48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG48" s="3">
         <v>300</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6000</v>
+        <v>5900</v>
       </c>
       <c r="E49" s="3">
         <v>6000</v>
       </c>
       <c r="F49" s="3">
-        <v>6300</v>
+        <v>6000</v>
       </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
         <v>5900</v>
       </c>
-      <c r="H49" s="3">
-        <v>5900</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
+        <v>900</v>
+      </c>
+      <c r="L49" s="3">
         <v>6000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>900</v>
-      </c>
-      <c r="K49" s="3">
-        <v>6000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>900</v>
       </c>
       <c r="M49" s="3">
         <v>900</v>
@@ -4513,8 +4624,8 @@
       <c r="AF49" s="3">
         <v>900</v>
       </c>
-      <c r="AG49" s="3" t="s">
-        <v>8</v>
+      <c r="AG49" s="3">
+        <v>900</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
@@ -4522,8 +4633,11 @@
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4623,8 +4737,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4724,31 +4841,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
-        <v>600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>600</v>
-      </c>
-      <c r="H52" s="3">
-        <v>600</v>
-      </c>
-      <c r="I52" s="3">
-        <v>600</v>
+        <v>100</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J52" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>600</v>
@@ -4775,7 +4895,7 @@
         <v>600</v>
       </c>
       <c r="S52" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="T52" s="3">
         <v>900</v>
@@ -4787,7 +4907,7 @@
         <v>900</v>
       </c>
       <c r="W52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="X52" s="3">
         <v>1200</v>
@@ -4802,7 +4922,7 @@
         <v>1200</v>
       </c>
       <c r="AB52" s="3">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="AC52" s="3">
         <v>600</v>
@@ -4811,13 +4931,13 @@
         <v>600</v>
       </c>
       <c r="AE52" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AF52" s="3">
         <v>300</v>
       </c>
-      <c r="AG52" s="3" t="s">
-        <v>8</v>
+      <c r="AG52" s="3">
+        <v>300</v>
       </c>
       <c r="AH52" s="3" t="s">
         <v>8</v>
@@ -4825,8 +4945,11 @@
       <c r="AI52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4926,109 +5049,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26200</v>
+      </c>
+      <c r="E54" s="3">
         <v>25700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26200</v>
       </c>
-      <c r="F54" s="3">
-        <v>29100</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" s="3">
         <v>28800</v>
       </c>
-      <c r="H54" s="3">
-        <v>29400</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
+        <v>26000</v>
+      </c>
+      <c r="L54" s="3">
         <v>31100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>26000</v>
       </c>
-      <c r="K54" s="3">
-        <v>31100</v>
-      </c>
-      <c r="L54" s="3">
-        <v>26000</v>
-      </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25300</v>
-      </c>
-      <c r="N54" s="3">
-        <v>24900</v>
       </c>
       <c r="O54" s="3">
         <v>24900</v>
       </c>
       <c r="P54" s="3">
+        <v>24900</v>
+      </c>
+      <c r="Q54" s="3">
         <v>22200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>23000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>21000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>20800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>19700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>19300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>18800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>16400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16900</v>
       </c>
-      <c r="AG54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5064,8 +5193,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5101,8 +5231,9 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5110,82 +5241,82 @@
         <v>1400</v>
       </c>
       <c r="E57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K57" s="3">
+        <v>500</v>
+      </c>
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>700</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>500</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>800</v>
-      </c>
-      <c r="N57" s="3">
-        <v>900</v>
       </c>
       <c r="O57" s="3">
         <v>900</v>
       </c>
       <c r="P57" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1900</v>
-      </c>
-      <c r="T57" s="3">
-        <v>1400</v>
       </c>
       <c r="U57" s="3">
         <v>1400</v>
       </c>
       <c r="V57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W57" s="3">
         <v>1000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1900</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>1300</v>
       </c>
       <c r="Z57" s="3">
         <v>1300</v>
       </c>
       <c r="AA57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB57" s="3">
         <v>900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>500</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>700</v>
       </c>
       <c r="AE57" s="3">
         <v>700</v>
@@ -5193,8 +5324,8 @@
       <c r="AF57" s="3">
         <v>700</v>
       </c>
-      <c r="AG57" s="3" t="s">
-        <v>8</v>
+      <c r="AG57" s="3">
+        <v>700</v>
       </c>
       <c r="AH57" s="3" t="s">
         <v>8</v>
@@ -5202,32 +5333,35 @@
       <c r="AI57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F58" s="3">
+        <v>700</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>600</v>
       </c>
-      <c r="E58" s="3">
-        <v>100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5249,14 +5383,14 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>700</v>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S58" s="3">
         <v>700</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
+      <c r="T58" s="3">
+        <v>700</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
@@ -5273,8 +5407,8 @@
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -5303,88 +5437,91 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4100</v>
+        <v>2100</v>
       </c>
       <c r="E59" s="3">
-        <v>3800</v>
+        <v>2400</v>
       </c>
       <c r="F59" s="3">
-        <v>3800</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H59" s="3">
-        <v>3900</v>
-      </c>
-      <c r="I59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="L59" s="3">
         <v>4000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>2400</v>
       </c>
-      <c r="K59" s="3">
-        <v>4000</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2400</v>
-      </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>1500</v>
       </c>
       <c r="O59" s="3">
         <v>1500</v>
       </c>
       <c r="P59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1600</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1800</v>
       </c>
       <c r="R59" s="3">
         <v>1800</v>
       </c>
       <c r="S59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T59" s="3">
         <v>1700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1900</v>
-      </c>
-      <c r="W59" s="3">
-        <v>1500</v>
       </c>
       <c r="X59" s="3">
         <v>1500</v>
       </c>
       <c r="Y59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1000</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>1100</v>
       </c>
       <c r="AD59" s="3">
         <v>1100</v>
@@ -5393,131 +5530,137 @@
         <v>1100</v>
       </c>
       <c r="AF59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AG59" s="3">
         <v>1300</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E60" s="3">
         <v>6100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4800</v>
       </c>
-      <c r="F60" s="3">
-        <v>4900</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="3">
         <v>4800</v>
       </c>
-      <c r="H60" s="3">
-        <v>4700</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L60" s="3">
         <v>5100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>3000</v>
       </c>
-      <c r="K60" s="3">
-        <v>5100</v>
-      </c>
-      <c r="L60" s="3">
-        <v>3000</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2200</v>
-      </c>
-      <c r="N60" s="3">
-        <v>2400</v>
       </c>
       <c r="O60" s="3">
         <v>2400</v>
       </c>
       <c r="P60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="Q60" s="3">
         <v>2600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1600</v>
-      </c>
-      <c r="AD60" s="3">
-        <v>1800</v>
       </c>
       <c r="AE60" s="3">
         <v>1800</v>
       </c>
       <c r="AF60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AG60" s="3">
         <v>2000</v>
       </c>
-      <c r="AG60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>1800</v>
       </c>
       <c r="E61" s="3">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -5529,7 +5672,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -5550,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>1600</v>
-      </c>
-      <c r="R61" s="3">
-        <v>900</v>
       </c>
       <c r="S61" s="3">
         <v>900</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -5580,13 +5723,13 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AB61" s="3">
         <v>500</v>
       </c>
       <c r="AC61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD61" s="3">
         <v>0</v>
@@ -5606,77 +5749,80 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="E62" s="3">
-        <v>3400</v>
+        <v>0</v>
       </c>
       <c r="F62" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G62" s="3">
-        <v>4500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>4500</v>
-      </c>
-      <c r="I62" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K62" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L62" s="3">
         <v>5300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>2800</v>
       </c>
-      <c r="K62" s="3">
-        <v>5300</v>
-      </c>
-      <c r="L62" s="3">
-        <v>2800</v>
-      </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3100</v>
-      </c>
-      <c r="N62" s="3">
-        <v>3000</v>
       </c>
       <c r="O62" s="3">
         <v>3000</v>
       </c>
       <c r="P62" s="3">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="Q62" s="3">
         <v>400</v>
       </c>
       <c r="R62" s="3">
+        <v>400</v>
+      </c>
+      <c r="S62" s="3">
         <v>500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>900</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5689,8 +5835,8 @@
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AD62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
@@ -5707,8 +5853,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5808,8 +5957,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5909,8 +6061,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6010,8 +6165,11 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6019,100 +6177,103 @@
         <v>8100</v>
       </c>
       <c r="E66" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F66" s="3">
         <v>8400</v>
       </c>
-      <c r="F66" s="3">
-        <v>9000</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" s="3">
         <v>9300</v>
       </c>
-      <c r="H66" s="3">
-        <v>9200</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
+        <v>5800</v>
+      </c>
+      <c r="L66" s="3">
         <v>10400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>5800</v>
       </c>
-      <c r="K66" s="3">
-        <v>10400</v>
-      </c>
-      <c r="L66" s="3">
-        <v>5800</v>
-      </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5200</v>
-      </c>
-      <c r="N66" s="3">
-        <v>5400</v>
       </c>
       <c r="O66" s="3">
         <v>5400</v>
       </c>
       <c r="P66" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Q66" s="3">
         <v>3000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>4200</v>
-      </c>
-      <c r="U66" s="3">
-        <v>4000</v>
       </c>
       <c r="V66" s="3">
         <v>4000</v>
       </c>
       <c r="W66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X66" s="3">
         <v>3400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1600</v>
-      </c>
-      <c r="AD66" s="3">
-        <v>1800</v>
       </c>
       <c r="AE66" s="3">
         <v>1800</v>
       </c>
       <c r="AF66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AG66" s="3">
         <v>2000</v>
       </c>
-      <c r="AG66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6148,8 +6309,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6249,8 +6411,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6350,8 +6515,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6451,8 +6619,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6552,109 +6723,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E72" s="3">
         <v>1200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1400</v>
       </c>
-      <c r="F72" s="3">
-        <v>3500</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3">
         <v>2800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>3200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>3600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>3200</v>
       </c>
-      <c r="K72" s="3">
-        <v>3600</v>
-      </c>
-      <c r="L72" s="3">
-        <v>3200</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3000</v>
-      </c>
-      <c r="N72" s="3">
-        <v>2300</v>
       </c>
       <c r="O72" s="3">
         <v>2300</v>
       </c>
       <c r="P72" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Q72" s="3">
         <v>1800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-500</v>
-      </c>
-      <c r="V72" s="3">
-        <v>-300</v>
       </c>
       <c r="W72" s="3">
         <v>-300</v>
       </c>
       <c r="X72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Y72" s="3">
         <v>-800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6754,8 +6931,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6855,8 +7035,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6956,109 +7139,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E76" s="3">
         <v>17500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3">
         <v>20000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>19500</v>
       </c>
-      <c r="H76" s="3">
-        <v>20200</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
+        <v>20300</v>
+      </c>
+      <c r="L76" s="3">
         <v>20700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>20300</v>
       </c>
-      <c r="K76" s="3">
-        <v>20700</v>
-      </c>
-      <c r="L76" s="3">
-        <v>20300</v>
-      </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20100</v>
-      </c>
-      <c r="N76" s="3">
-        <v>19500</v>
       </c>
       <c r="O76" s="3">
         <v>19500</v>
       </c>
       <c r="P76" s="3">
+        <v>19500</v>
+      </c>
+      <c r="Q76" s="3">
         <v>19200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>17400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17100</v>
-      </c>
-      <c r="V76" s="3">
-        <v>17500</v>
       </c>
       <c r="W76" s="3">
         <v>17500</v>
       </c>
       <c r="X76" s="3">
+        <v>17500</v>
+      </c>
+      <c r="Y76" s="3">
         <v>16900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14800</v>
       </c>
-      <c r="AG76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AI76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7158,215 +7347,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
-        <v>45291</v>
-      </c>
       <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44926</v>
       </c>
       <c r="J80" s="2">
         <v>44834</v>
       </c>
       <c r="K80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>800</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1100</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>700</v>
       </c>
       <c r="J81" s="3">
         <v>-300</v>
       </c>
       <c r="K81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L81" s="3">
         <v>-400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-400</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
       <c r="U81" s="3">
+        <v>0</v>
+      </c>
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7402,82 +7600,83 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
-        <v>200</v>
-      </c>
-      <c r="F83" s="3">
-        <v>500</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>100</v>
-      </c>
-      <c r="J83" s="3">
-        <v>100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>200</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
-      </c>
-      <c r="X83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -7503,8 +7702,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7604,8 +7806,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7705,8 +7910,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7806,8 +8014,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7907,8 +8118,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8008,80 +8222,83 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1400</v>
       </c>
-      <c r="G89" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>-800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3700</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>8</v>
       </c>
@@ -8091,8 +8308,8 @@
       <c r="AC89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD89" s="3">
-        <v>0</v>
+      <c r="AD89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE89" s="3">
         <v>0</v>
@@ -8109,8 +8326,11 @@
       <c r="AI89" s="3">
         <v>0</v>
       </c>
+      <c r="AJ89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8146,31 +8366,32 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
+        <v>0</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
       <c r="I91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -8211,17 +8432,17 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -8247,8 +8468,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8348,8 +8572,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8449,34 +8676,37 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
       </c>
       <c r="F94" s="3">
-        <v>-700</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-200</v>
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
+      <c r="I94" s="3">
+        <v>-200</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -8514,17 +8744,17 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z94" s="3">
         <v>100</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -8550,8 +8780,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8587,31 +8820,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-100</v>
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8688,8 +8922,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8789,8 +9026,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8890,8 +9130,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8991,34 +9234,37 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-200</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -9056,17 +9302,17 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-300</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>0</v>
+      <c r="AA100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
@@ -9092,31 +9338,34 @@
       <c r="AI100" s="3">
         <v>0</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9193,34 +9442,37 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>600</v>
       </c>
-      <c r="F102" s="3">
-        <v>-3000</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1400</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K102" s="3">
-        <v>0</v>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L102" s="3">
         <v>0</v>
@@ -9258,17 +9510,17 @@
       <c r="W102" s="3">
         <v>0</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="3">
         <v>3600</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA102" s="3">
-        <v>0</v>
+      <c r="AA102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB102" s="3">
         <v>0</v>
@@ -9292,6 +9544,9 @@
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
   <si>
     <t>ORBT</t>
   </si>
@@ -656,468 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
-      </c>
-      <c r="I7" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44834</v>
       </c>
       <c r="K7" s="2">
         <v>44834</v>
       </c>
       <c r="L7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E8" s="3">
         <v>8400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>7200</v>
+      </c>
+      <c r="I8" s="3">
         <v>8200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>7000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>5200</v>
-      </c>
-      <c r="J8" s="3">
-        <v>6000</v>
       </c>
       <c r="K8" s="3">
         <v>6000</v>
       </c>
       <c r="L8" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M8" s="3">
         <v>5800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>24700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>20900</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>5000</v>
       </c>
       <c r="AF8" s="3">
         <v>5000</v>
       </c>
       <c r="AG8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AH8" s="3">
         <v>5200</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>5500</v>
       </c>
       <c r="AI8" s="3">
         <v>5500</v>
       </c>
       <c r="AJ8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AK8" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E9" s="3">
         <v>5300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J9" s="3">
         <v>4700</v>
-      </c>
-      <c r="I9" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J9" s="3">
-        <v>4100</v>
       </c>
       <c r="K9" s="3">
         <v>4100</v>
       </c>
       <c r="L9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="M9" s="3">
         <v>4200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>16500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2900</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>3200</v>
       </c>
       <c r="AG9" s="3">
         <v>3200</v>
       </c>
       <c r="AH9" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AI9" s="3">
         <v>3300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3100</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1900</v>
       </c>
       <c r="F10" s="3">
         <v>1900</v>
       </c>
       <c r="G10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I10" s="3">
         <v>3200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>1700</v>
       </c>
       <c r="R10" s="3">
         <v>1700</v>
       </c>
       <c r="S10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T10" s="3">
         <v>2500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>8200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>8200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1154,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1258,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1362,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1385,8 +1403,8 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1395,41 +1413,41 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-1600</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>100</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1445,8 +1463,8 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
@@ -1457,8 +1475,8 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
+      <c r="AH14" s="3">
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
@@ -1466,13 +1484,16 @@
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1481,7 +1502,7 @@
         <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1490,7 +1511,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1570,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1605,31 +1629,32 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E17" s="3">
         <v>7800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I17" s="3">
         <v>7400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>7100</v>
-      </c>
-      <c r="I17" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>6300</v>
       </c>
       <c r="K17" s="3">
         <v>6300</v>
@@ -1638,183 +1663,189 @@
         <v>6300</v>
       </c>
       <c r="M17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="N17" s="3">
         <v>6400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>23000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>19300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>300</v>
+      </c>
+      <c r="E18" s="3">
         <v>600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I18" s="3">
         <v>800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-300</v>
       </c>
       <c r="K18" s="3">
         <v>-300</v>
       </c>
       <c r="L18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M18" s="3">
         <v>-500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
-        <v>0</v>
-      </c>
       <c r="X18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3">
         <v>600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>1700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1851,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1860,34 +1892,34 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1902,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
         <v>-100</v>
@@ -1911,7 +1943,7 @@
         <v>-100</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -1935,11 +1967,11 @@
         <v>0</v>
       </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
@@ -1955,83 +1987,86 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>400</v>
+      </c>
+      <c r="E21" s="3">
         <v>700</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I21" s="3">
         <v>900</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1000</v>
       </c>
       <c r="J21" s="3">
         <v>-300</v>
       </c>
       <c r="K21" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="L21" s="3">
         <v>-200</v>
       </c>
       <c r="M21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N21" s="3">
         <v>500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-100</v>
       </c>
-      <c r="W21" s="3">
-        <v>0</v>
-      </c>
       <c r="X21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3">
         <v>600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1800</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2059,13 +2094,16 @@
       <c r="AJ21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -2082,20 +2120,20 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -2103,11 +2141,11 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -2115,11 +2153,11 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2127,11 +2165,11 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -2139,11 +2177,11 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2163,120 +2201,126 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>200</v>
+      </c>
+      <c r="E23" s="3">
         <v>600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-400</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-300</v>
       </c>
       <c r="K23" s="3">
         <v>-300</v>
       </c>
       <c r="L23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M23" s="3">
         <v>-400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-400</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
       <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>-200</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -2339,40 +2383,43 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-500</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-600</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-300</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
         <v>0</v>
       </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-300</v>
       </c>
-      <c r="AI24" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2475,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-500</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-300</v>
       </c>
       <c r="K26" s="3">
         <v>-300</v>
       </c>
       <c r="L26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
       <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I27" s="3">
         <v>800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-300</v>
       </c>
       <c r="K27" s="3">
         <v>-300</v>
       </c>
       <c r="L27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
       <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2787,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2891,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2995,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3099,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3108,34 +3176,34 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -3150,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T32" s="3">
         <v>100</v>
@@ -3159,7 +3227,7 @@
         <v>100</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -3183,11 +3251,11 @@
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
@@ -3203,112 +3271,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-300</v>
       </c>
       <c r="K33" s="3">
         <v>-300</v>
       </c>
       <c r="L33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
       <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3411,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-300</v>
       </c>
       <c r="K35" s="3">
         <v>-300</v>
       </c>
       <c r="L35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
       <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
-      </c>
-      <c r="I38" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44834</v>
       </c>
       <c r="K38" s="2">
         <v>44834</v>
       </c>
       <c r="L38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3662,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3700,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1800</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>8</v>
+      <c r="H41" s="3">
+        <v>1300</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K41" s="3">
         <v>3400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8300</v>
-      </c>
-      <c r="O41" s="3">
-        <v>6900</v>
       </c>
       <c r="P41" s="3">
         <v>6900</v>
       </c>
       <c r="Q41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="R41" s="3">
         <v>7000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1100</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>900</v>
       </c>
       <c r="AD41" s="3">
         <v>900</v>
       </c>
       <c r="AE41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF41" s="3">
         <v>800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1900</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3888,19 +3976,19 @@
         <v>0</v>
       </c>
       <c r="AD42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AE42" s="3">
         <v>300</v>
       </c>
       <c r="AF42" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AG42" s="3">
         <v>200</v>
       </c>
-      <c r="AH42" s="3" t="s">
-        <v>8</v>
+      <c r="AH42" s="3">
+        <v>200</v>
       </c>
       <c r="AI42" s="3" t="s">
         <v>8</v>
@@ -3908,64 +3996,67 @@
       <c r="AJ42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E43" s="3">
         <v>5300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3200</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
+      <c r="H43" s="3">
+        <v>4000</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>4000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3300</v>
-      </c>
-      <c r="O43" s="3">
-        <v>3700</v>
       </c>
       <c r="P43" s="3">
         <v>3700</v>
       </c>
       <c r="Q43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="R43" s="3">
         <v>3300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3700</v>
-      </c>
-      <c r="U43" s="3">
-        <v>3800</v>
       </c>
       <c r="V43" s="3">
         <v>3800</v>
@@ -3974,132 +4065,135 @@
         <v>3800</v>
       </c>
       <c r="X43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y43" s="3">
         <v>3700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>4300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3000</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E44" s="3">
         <v>10400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10100</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>8</v>
+      <c r="H44" s="3">
+        <v>10000</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
         <v>10600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>11800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8400</v>
-      </c>
-      <c r="O44" s="3">
-        <v>9000</v>
       </c>
       <c r="P44" s="3">
         <v>9000</v>
       </c>
       <c r="Q44" s="3">
-        <v>9400</v>
+        <v>9000</v>
       </c>
       <c r="R44" s="3">
         <v>9400</v>
       </c>
       <c r="S44" s="3">
+        <v>9400</v>
+      </c>
+      <c r="T44" s="3">
         <v>10000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>10800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>11200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>10500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>10300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>10000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>10700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>10100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>11400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>10900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>9600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>10100</v>
-      </c>
-      <c r="AE44" s="3">
-        <v>10000</v>
       </c>
       <c r="AF44" s="3">
         <v>10000</v>
@@ -4107,8 +4201,8 @@
       <c r="AG44" s="3">
         <v>10000</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>8</v>
+      <c r="AH44" s="3">
+        <v>10000</v>
       </c>
       <c r="AI44" s="3" t="s">
         <v>8</v>
@@ -4116,8 +4210,11 @@
       <c r="AJ44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4128,22 +4225,22 @@
         <v>400</v>
       </c>
       <c r="F45" s="3">
+        <v>400</v>
+      </c>
+      <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
+      <c r="H45" s="3">
+        <v>400</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>1000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>400</v>
       </c>
       <c r="L45" s="3">
         <v>400</v>
@@ -4155,19 +4252,19 @@
         <v>400</v>
       </c>
       <c r="O45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="P45" s="3">
         <v>300</v>
       </c>
       <c r="Q45" s="3">
+        <v>300</v>
+      </c>
+      <c r="R45" s="3">
         <v>400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>400</v>
       </c>
       <c r="T45" s="3">
         <v>400</v>
@@ -4176,16 +4273,16 @@
         <v>400</v>
       </c>
       <c r="V45" s="3">
+        <v>400</v>
+      </c>
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>300</v>
       </c>
       <c r="Z45" s="3">
         <v>300</v>
@@ -4194,138 +4291,144 @@
         <v>300</v>
       </c>
       <c r="AB45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC45" s="3">
         <v>900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>300</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E46" s="3">
         <v>16400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15700</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>8</v>
+      <c r="H46" s="3">
+        <v>15800</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3">
         <v>19000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20400</v>
-      </c>
-      <c r="O46" s="3">
-        <v>19800</v>
       </c>
       <c r="P46" s="3">
         <v>19800</v>
       </c>
       <c r="Q46" s="3">
+        <v>19800</v>
+      </c>
+      <c r="R46" s="3">
         <v>20100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>20100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>19300</v>
-      </c>
-      <c r="U46" s="3">
-        <v>18200</v>
       </c>
       <c r="V46" s="3">
         <v>18200</v>
       </c>
       <c r="W46" s="3">
+        <v>18200</v>
+      </c>
+      <c r="X46" s="3">
         <v>18500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15400</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4350,8 +4453,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4428,79 +4531,82 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3800</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>8</v>
+      <c r="H48" s="3">
+        <v>3900</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J48" s="3">
-        <v>3300</v>
+      <c r="J48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K48" s="3">
         <v>3300</v>
       </c>
       <c r="L48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="M48" s="3">
         <v>3400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3400</v>
-      </c>
-      <c r="O48" s="3">
-        <v>3600</v>
       </c>
       <c r="P48" s="3">
         <v>3600</v>
       </c>
       <c r="Q48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="R48" s="3">
         <v>700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1100</v>
       </c>
       <c r="U48" s="3">
         <v>1100</v>
       </c>
       <c r="V48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="W48" s="3">
         <v>1200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1500</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>300</v>
       </c>
       <c r="AA48" s="3">
         <v>300</v>
@@ -4512,7 +4618,7 @@
         <v>300</v>
       </c>
       <c r="AD48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE48" s="3">
         <v>200</v>
@@ -4521,51 +4627,54 @@
         <v>200</v>
       </c>
       <c r="AG48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH48" s="3">
         <v>300</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E49" s="3">
         <v>5900</v>
-      </c>
-      <c r="E49" s="3">
-        <v>6000</v>
       </c>
       <c r="F49" s="3">
         <v>6000</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
+        <v>6100</v>
       </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>5900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>900</v>
       </c>
       <c r="N49" s="3">
         <v>900</v>
@@ -4627,8 +4736,8 @@
       <c r="AG49" s="3">
         <v>900</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>8</v>
+      <c r="AH49" s="3">
+        <v>900</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>8</v>
@@ -4636,8 +4745,11 @@
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4740,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4844,8 +4959,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4858,20 +4976,20 @@
       <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
+      <c r="G52" s="3">
+        <v>100</v>
+      </c>
+      <c r="H52" s="3">
+        <v>100</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L52" s="3">
         <v>600</v>
@@ -4898,7 +5016,7 @@
         <v>600</v>
       </c>
       <c r="T52" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="U52" s="3">
         <v>900</v>
@@ -4910,7 +5028,7 @@
         <v>900</v>
       </c>
       <c r="X52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="Y52" s="3">
         <v>1200</v>
@@ -4925,7 +5043,7 @@
         <v>1200</v>
       </c>
       <c r="AC52" s="3">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="AD52" s="3">
         <v>600</v>
@@ -4934,13 +5052,13 @@
         <v>600</v>
       </c>
       <c r="AF52" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AG52" s="3">
         <v>300</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>8</v>
+      <c r="AH52" s="3">
+        <v>300</v>
       </c>
       <c r="AI52" s="3" t="s">
         <v>8</v>
@@ -4948,8 +5066,11 @@
       <c r="AJ52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5052,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E54" s="3">
         <v>26200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>25700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26200</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>8</v>
+      <c r="H54" s="3">
+        <v>26400</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K54" s="3">
         <v>28800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>26000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25300</v>
-      </c>
-      <c r="O54" s="3">
-        <v>24900</v>
       </c>
       <c r="P54" s="3">
         <v>24900</v>
       </c>
       <c r="Q54" s="3">
+        <v>24900</v>
+      </c>
+      <c r="R54" s="3">
         <v>22200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>23000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>20800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>21100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>19700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>18800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>16900</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5194,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5232,94 +5360,95 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1400</v>
+        <v>900</v>
       </c>
       <c r="E57" s="3">
         <v>1400</v>
       </c>
       <c r="F57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
+      <c r="H57" s="3">
+        <v>1100</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>800</v>
-      </c>
-      <c r="O57" s="3">
-        <v>900</v>
       </c>
       <c r="P57" s="3">
         <v>900</v>
       </c>
       <c r="Q57" s="3">
+        <v>900</v>
+      </c>
+      <c r="R57" s="3">
         <v>1000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1900</v>
-      </c>
-      <c r="U57" s="3">
-        <v>1400</v>
       </c>
       <c r="V57" s="3">
         <v>1400</v>
       </c>
       <c r="W57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="X57" s="3">
         <v>1000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1900</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>1300</v>
       </c>
       <c r="AA57" s="3">
         <v>1300</v>
       </c>
       <c r="AB57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AC57" s="3">
         <v>900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>500</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>700</v>
       </c>
       <c r="AF57" s="3">
         <v>700</v>
@@ -5327,8 +5456,8 @@
       <c r="AG57" s="3">
         <v>700</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>8</v>
+      <c r="AH57" s="3">
+        <v>700</v>
       </c>
       <c r="AI57" s="3" t="s">
         <v>8</v>
@@ -5336,8 +5465,11 @@
       <c r="AJ57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5345,26 +5477,26 @@
         <v>1700</v>
       </c>
       <c r="E58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="F58" s="3">
         <v>1200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>700</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>600</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5386,14 +5518,14 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>700</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>700</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
+      <c r="U58" s="3">
+        <v>700</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
@@ -5410,8 +5542,8 @@
       <c r="Z58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5440,91 +5572,94 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E59" s="3">
         <v>2100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1900</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>8</v>
+      <c r="H59" s="3">
+        <v>1300</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K59" s="3">
         <v>2300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1500</v>
       </c>
       <c r="P59" s="3">
         <v>1500</v>
       </c>
       <c r="Q59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R59" s="3">
         <v>1600</v>
-      </c>
-      <c r="R59" s="3">
-        <v>1800</v>
       </c>
       <c r="S59" s="3">
         <v>1800</v>
       </c>
       <c r="T59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="U59" s="3">
         <v>1700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1900</v>
-      </c>
-      <c r="X59" s="3">
-        <v>1500</v>
       </c>
       <c r="Y59" s="3">
         <v>1500</v>
       </c>
       <c r="Z59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA59" s="3">
         <v>1400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1000</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>1100</v>
       </c>
       <c r="AE59" s="3">
         <v>1100</v>
@@ -5533,123 +5668,129 @@
         <v>1100</v>
       </c>
       <c r="AG59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AH59" s="3">
         <v>1300</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E60" s="3">
         <v>6300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4800</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>8</v>
+      <c r="H60" s="3">
+        <v>4200</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K60" s="3">
         <v>4800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2200</v>
-      </c>
-      <c r="O60" s="3">
-        <v>2400</v>
       </c>
       <c r="P60" s="3">
         <v>2400</v>
       </c>
       <c r="Q60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="R60" s="3">
         <v>2600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1600</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>1800</v>
       </c>
       <c r="AF60" s="3">
         <v>1800</v>
       </c>
       <c r="AG60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AH60" s="3">
         <v>2000</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5657,26 +5798,26 @@
         <v>1800</v>
       </c>
       <c r="E61" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F61" s="3">
         <v>2000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2200</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>2300</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5696,16 +5837,16 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>1600</v>
-      </c>
-      <c r="S61" s="3">
-        <v>900</v>
       </c>
       <c r="T61" s="3">
         <v>900</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -5726,13 +5867,13 @@
         <v>0</v>
       </c>
       <c r="AB61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AC61" s="3">
         <v>500</v>
       </c>
       <c r="AD61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AE61" s="3">
         <v>0</v>
@@ -5752,80 +5893,83 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
       </c>
       <c r="F62" s="3">
+        <v>0</v>
+      </c>
+      <c r="G62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>8</v>
+      <c r="H62" s="3">
+        <v>1400</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
         <v>2200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3100</v>
-      </c>
-      <c r="O62" s="3">
-        <v>3000</v>
       </c>
       <c r="P62" s="3">
         <v>3000</v>
       </c>
       <c r="Q62" s="3">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="R62" s="3">
         <v>400</v>
       </c>
       <c r="S62" s="3">
+        <v>400</v>
+      </c>
+      <c r="T62" s="3">
         <v>500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>900</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5838,8 +5982,8 @@
       <c r="AD62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -5856,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5960,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6064,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6168,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8100</v>
+        <v>7000</v>
       </c>
       <c r="E66" s="3">
         <v>8100</v>
       </c>
       <c r="F66" s="3">
+        <v>8100</v>
+      </c>
+      <c r="G66" s="3">
         <v>8400</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>8</v>
+      <c r="H66" s="3">
+        <v>7900</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K66" s="3">
         <v>9300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5200</v>
-      </c>
-      <c r="O66" s="3">
-        <v>5400</v>
       </c>
       <c r="P66" s="3">
         <v>5400</v>
       </c>
       <c r="Q66" s="3">
+        <v>5400</v>
+      </c>
+      <c r="R66" s="3">
         <v>3000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>4200</v>
-      </c>
-      <c r="V66" s="3">
-        <v>4000</v>
       </c>
       <c r="W66" s="3">
         <v>4000</v>
       </c>
       <c r="X66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Y66" s="3">
         <v>3400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>4200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1600</v>
-      </c>
-      <c r="AE66" s="3">
-        <v>1800</v>
       </c>
       <c r="AF66" s="3">
         <v>1800</v>
       </c>
       <c r="AG66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AH66" s="3">
         <v>2000</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6310,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6414,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6518,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6622,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6726,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E72" s="3">
         <v>1700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1400</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
+      <c r="H72" s="3">
+        <v>2200</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>2800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3000</v>
-      </c>
-      <c r="O72" s="3">
-        <v>2300</v>
       </c>
       <c r="P72" s="3">
         <v>2300</v>
       </c>
       <c r="Q72" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R72" s="3">
         <v>1800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-500</v>
-      </c>
-      <c r="W72" s="3">
-        <v>-300</v>
       </c>
       <c r="X72" s="3">
         <v>-300</v>
       </c>
       <c r="Y72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-4700</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6934,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7038,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7142,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E76" s="3">
         <v>18100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17700</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I76" s="3">
-        <v>20000</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="H76" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K76" s="3">
         <v>19500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>20300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20100</v>
-      </c>
-      <c r="O76" s="3">
-        <v>19500</v>
       </c>
       <c r="P76" s="3">
         <v>19500</v>
       </c>
       <c r="Q76" s="3">
+        <v>19500</v>
+      </c>
+      <c r="R76" s="3">
         <v>19200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>17400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17100</v>
-      </c>
-      <c r="W76" s="3">
-        <v>17500</v>
       </c>
       <c r="X76" s="3">
         <v>17500</v>
       </c>
       <c r="Y76" s="3">
+        <v>17500</v>
+      </c>
+      <c r="Z76" s="3">
         <v>16900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14800</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7350,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
-      </c>
-      <c r="I80" s="2">
-        <v>45016</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44834</v>
       </c>
       <c r="K80" s="2">
         <v>44834</v>
       </c>
       <c r="L80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-300</v>
       </c>
       <c r="K81" s="3">
         <v>-300</v>
       </c>
       <c r="L81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
       <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7601,23 +7797,24 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H83" s="3" t="s">
         <v>8</v>
       </c>
@@ -7627,15 +7824,15 @@
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -7648,8 +7845,8 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>8</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>8</v>
@@ -7666,20 +7863,20 @@
       <c r="W83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="X83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA83" s="3">
         <v>100</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -7705,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7809,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7913,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8017,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8121,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8225,83 +8437,86 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>700</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>-800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3700</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB89" s="3" t="s">
         <v>8</v>
       </c>
@@ -8311,8 +8526,8 @@
       <c r="AD89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
+      <c r="AE89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF89" s="3">
         <v>0</v>
@@ -8329,8 +8544,11 @@
       <c r="AJ89" s="3">
         <v>0</v>
       </c>
+      <c r="AK89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8367,85 +8585,86 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AA91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -8471,8 +8690,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8575,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8679,37 +8904,40 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
+      <c r="E94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
+      <c r="L94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M94" s="3">
         <v>0</v>
@@ -8747,17 +8975,17 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA94" s="3">
         <v>100</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -8783,8 +9011,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8821,34 +9052,35 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3">
         <v>100</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8925,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9029,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9133,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9237,37 +9478,40 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
+      <c r="L100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M100" s="3">
         <v>0</v>
@@ -9305,17 +9549,17 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-300</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
+      <c r="AB100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
@@ -9341,8 +9585,11 @@
       <c r="AJ100" s="3">
         <v>0</v>
       </c>
+      <c r="AK100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9367,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9445,8 +9692,11 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9454,28 +9704,28 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L102" s="3">
-        <v>0</v>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M102" s="3">
         <v>0</v>
@@ -9513,17 +9763,17 @@
       <c r="X102" s="3">
         <v>0</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA102" s="3">
         <v>3600</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB102" s="3">
-        <v>0</v>
+      <c r="AB102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC102" s="3">
         <v>0</v>
@@ -9547,6 +9797,9 @@
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>ORBT</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
-      </c>
-      <c r="K7" s="2">
-        <v>44834</v>
       </c>
       <c r="L7" s="2">
         <v>44834</v>
       </c>
       <c r="M7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E8" s="3">
         <v>8700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7000</v>
-      </c>
-      <c r="K8" s="3">
-        <v>6000</v>
       </c>
       <c r="L8" s="3">
         <v>6000</v>
       </c>
       <c r="M8" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N8" s="3">
         <v>5800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>7900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>24700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>20900</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>5000</v>
       </c>
       <c r="AG8" s="3">
         <v>5000</v>
       </c>
       <c r="AH8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AI8" s="3">
         <v>5200</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>5500</v>
       </c>
       <c r="AJ8" s="3">
         <v>5500</v>
       </c>
       <c r="AK8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AL8" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E9" s="3">
         <v>5700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4300</v>
-      </c>
-      <c r="H9" s="3">
-        <v>5000</v>
       </c>
       <c r="I9" s="3">
         <v>5000</v>
       </c>
       <c r="J9" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K9" s="3">
         <v>4700</v>
-      </c>
-      <c r="K9" s="3">
-        <v>4100</v>
       </c>
       <c r="L9" s="3">
         <v>4100</v>
       </c>
       <c r="M9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="N9" s="3">
         <v>4200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>16500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2900</v>
-      </c>
-      <c r="AG9" s="3">
-        <v>3200</v>
       </c>
       <c r="AH9" s="3">
         <v>3200</v>
       </c>
       <c r="AI9" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AJ9" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
         <v>3000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1900</v>
       </c>
       <c r="G10" s="3">
         <v>1900</v>
       </c>
       <c r="H10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I10" s="3">
         <v>2200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2200</v>
-      </c>
-      <c r="R10" s="3">
-        <v>1700</v>
       </c>
       <c r="S10" s="3">
         <v>1700</v>
       </c>
       <c r="T10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U10" s="3">
         <v>2500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>8200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>8200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1406,8 +1426,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1416,41 +1436,41 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-1600</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1466,8 +1486,8 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1478,8 +1498,8 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
+      <c r="AI14" s="3">
+        <v>0</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
@@ -1487,16 +1507,19 @@
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>200</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>200</v>
       </c>
       <c r="F15" s="3">
         <v>200</v>
@@ -1505,7 +1528,7 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="3">
         <v>100</v>
@@ -1514,7 +1537,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,34 +1656,35 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E17" s="3">
         <v>8400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7100</v>
-      </c>
-      <c r="K17" s="3">
-        <v>6300</v>
       </c>
       <c r="L17" s="3">
         <v>6300</v>
@@ -1666,186 +1693,192 @@
         <v>6300</v>
       </c>
       <c r="N17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="O17" s="3">
         <v>6400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>23000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>19300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E18" s="3">
         <v>300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-300</v>
       </c>
       <c r="L18" s="3">
         <v>-300</v>
       </c>
       <c r="M18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N18" s="3">
         <v>-500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
-        <v>0</v>
-      </c>
       <c r="Y18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3">
         <v>600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>1700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>1600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1895,34 +1929,34 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1937,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
         <v>-100</v>
@@ -1946,7 +1980,7 @@
         <v>-100</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
@@ -1970,11 +2004,11 @@
         <v>0</v>
       </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
@@ -1990,86 +2024,89 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E21" s="3">
         <v>400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>700</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
       <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
         <v>-600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-300</v>
       </c>
       <c r="K21" s="3">
         <v>-300</v>
       </c>
       <c r="L21" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="M21" s="3">
         <v>-200</v>
       </c>
       <c r="N21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O21" s="3">
         <v>500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-100</v>
       </c>
-      <c r="X21" s="3">
-        <v>0</v>
-      </c>
       <c r="Y21" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3">
         <v>600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1800</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2097,17 +2134,20 @@
       <c r="AK21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
@@ -2123,20 +2163,20 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2144,11 +2184,11 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -2156,11 +2196,11 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2168,11 +2208,11 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -2180,11 +2220,11 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2204,126 +2244,132 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E23" s="3">
         <v>200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-300</v>
       </c>
       <c r="L23" s="3">
         <v>-300</v>
       </c>
       <c r="M23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N23" s="3">
         <v>-400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-400</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>-200</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
       <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
         <v>600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -2386,40 +2432,43 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-500</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
-      </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-600</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-300</v>
       </c>
-      <c r="AG24" s="3">
-        <v>0</v>
-      </c>
       <c r="AH24" s="3">
         <v>0</v>
       </c>
       <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ24" s="3">
-        <v>0</v>
-      </c>
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-300</v>
       </c>
       <c r="L26" s="3">
         <v>-300</v>
       </c>
       <c r="M26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-300</v>
       </c>
       <c r="L27" s="3">
         <v>-300</v>
       </c>
       <c r="M27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3179,34 +3249,34 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -3221,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="T32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U32" s="3">
         <v>100</v>
@@ -3230,7 +3300,7 @@
         <v>100</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
@@ -3254,11 +3324,11 @@
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
@@ -3274,115 +3344,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>-300</v>
       </c>
       <c r="L33" s="3">
         <v>-300</v>
       </c>
       <c r="M33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>-300</v>
       </c>
       <c r="L35" s="3">
         <v>-300</v>
       </c>
       <c r="M35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
-      </c>
-      <c r="K38" s="2">
-        <v>44834</v>
       </c>
       <c r="L38" s="2">
         <v>44834</v>
       </c>
       <c r="M38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1300</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L41" s="3">
         <v>3400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8300</v>
-      </c>
-      <c r="P41" s="3">
-        <v>6900</v>
       </c>
       <c r="Q41" s="3">
         <v>6900</v>
       </c>
       <c r="R41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="S41" s="3">
         <v>7000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1100</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>900</v>
       </c>
       <c r="AE41" s="3">
         <v>900</v>
       </c>
       <c r="AF41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG41" s="3">
         <v>800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1900</v>
       </c>
-      <c r="AI41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3979,19 +4069,19 @@
         <v>0</v>
       </c>
       <c r="AE42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF42" s="3">
         <v>300</v>
       </c>
       <c r="AG42" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AH42" s="3">
         <v>200</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>8</v>
+      <c r="AI42" s="3">
+        <v>200</v>
       </c>
       <c r="AJ42" s="3" t="s">
         <v>8</v>
@@ -3999,67 +4089,70 @@
       <c r="AK42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E43" s="3">
         <v>4600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
         <v>4000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3300</v>
-      </c>
-      <c r="P43" s="3">
-        <v>3700</v>
       </c>
       <c r="Q43" s="3">
         <v>3700</v>
       </c>
       <c r="R43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="S43" s="3">
         <v>3300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>4000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3700</v>
-      </c>
-      <c r="V43" s="3">
-        <v>3800</v>
       </c>
       <c r="W43" s="3">
         <v>3800</v>
@@ -4068,135 +4161,138 @@
         <v>3800</v>
       </c>
       <c r="Y43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Z43" s="3">
         <v>3700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>4300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3000</v>
       </c>
-      <c r="AI43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E44" s="3">
         <v>8900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10000</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3">
         <v>10600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>11800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8400</v>
-      </c>
-      <c r="P44" s="3">
-        <v>9000</v>
       </c>
       <c r="Q44" s="3">
         <v>9000</v>
       </c>
       <c r="R44" s="3">
-        <v>9400</v>
+        <v>9000</v>
       </c>
       <c r="S44" s="3">
         <v>9400</v>
       </c>
       <c r="T44" s="3">
+        <v>9400</v>
+      </c>
+      <c r="U44" s="3">
         <v>10000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>10800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>11200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>10500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>10300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>10000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>10700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>10100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>11400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>10900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>9600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>10100</v>
-      </c>
-      <c r="AF44" s="3">
-        <v>10000</v>
       </c>
       <c r="AG44" s="3">
         <v>10000</v>
@@ -4204,8 +4300,8 @@
       <c r="AH44" s="3">
         <v>10000</v>
       </c>
-      <c r="AI44" s="3" t="s">
-        <v>8</v>
+      <c r="AI44" s="3">
+        <v>10000</v>
       </c>
       <c r="AJ44" s="3" t="s">
         <v>8</v>
@@ -4213,8 +4309,11 @@
       <c r="AK44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4228,22 +4327,22 @@
         <v>400</v>
       </c>
       <c r="G45" s="3">
+        <v>400</v>
+      </c>
+      <c r="H45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>1000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>400</v>
       </c>
       <c r="M45" s="3">
         <v>400</v>
@@ -4255,19 +4354,19 @@
         <v>400</v>
       </c>
       <c r="P45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Q45" s="3">
         <v>300</v>
       </c>
       <c r="R45" s="3">
+        <v>300</v>
+      </c>
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
-      </c>
-      <c r="T45" s="3">
-        <v>400</v>
       </c>
       <c r="U45" s="3">
         <v>400</v>
@@ -4276,16 +4375,16 @@
         <v>400</v>
       </c>
       <c r="W45" s="3">
+        <v>400</v>
+      </c>
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>300</v>
       </c>
       <c r="AA45" s="3">
         <v>300</v>
@@ -4294,141 +4393,147 @@
         <v>300</v>
       </c>
       <c r="AC45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD45" s="3">
         <v>900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>300</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E46" s="3">
         <v>15200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>16400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>15500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>15700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15800</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L46" s="3">
         <v>19000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>20400</v>
-      </c>
-      <c r="P46" s="3">
-        <v>19800</v>
       </c>
       <c r="Q46" s="3">
         <v>19800</v>
       </c>
       <c r="R46" s="3">
+        <v>19800</v>
+      </c>
+      <c r="S46" s="3">
         <v>20100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>20600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>20100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>19300</v>
-      </c>
-      <c r="V46" s="3">
-        <v>18200</v>
       </c>
       <c r="W46" s="3">
         <v>18200</v>
       </c>
       <c r="X46" s="3">
+        <v>18200</v>
+      </c>
+      <c r="Y46" s="3">
         <v>18500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>15400</v>
       </c>
-      <c r="AI46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4456,8 +4561,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4534,82 +4639,85 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E48" s="3">
         <v>3600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3900</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K48" s="3">
-        <v>3300</v>
+      <c r="K48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L48" s="3">
         <v>3300</v>
       </c>
       <c r="M48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N48" s="3">
         <v>3400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3400</v>
-      </c>
-      <c r="P48" s="3">
-        <v>3600</v>
       </c>
       <c r="Q48" s="3">
         <v>3600</v>
       </c>
       <c r="R48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="S48" s="3">
         <v>700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1000</v>
-      </c>
-      <c r="U48" s="3">
-        <v>1100</v>
       </c>
       <c r="V48" s="3">
         <v>1100</v>
       </c>
       <c r="W48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="X48" s="3">
         <v>1200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1500</v>
-      </c>
-      <c r="AA48" s="3">
-        <v>300</v>
       </c>
       <c r="AB48" s="3">
         <v>300</v>
@@ -4621,7 +4729,7 @@
         <v>300</v>
       </c>
       <c r="AE48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AF48" s="3">
         <v>200</v>
@@ -4630,19 +4738,22 @@
         <v>200</v>
       </c>
       <c r="AH48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AI48" s="3">
         <v>300</v>
       </c>
-      <c r="AI48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4650,34 +4761,34 @@
         <v>5800</v>
       </c>
       <c r="E49" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F49" s="3">
         <v>5900</v>
-      </c>
-      <c r="F49" s="3">
-        <v>6000</v>
       </c>
       <c r="G49" s="3">
         <v>6000</v>
       </c>
       <c r="H49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I49" s="3">
         <v>6100</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
         <v>5900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>900</v>
       </c>
       <c r="O49" s="3">
         <v>900</v>
@@ -4739,8 +4850,8 @@
       <c r="AH49" s="3">
         <v>900</v>
       </c>
-      <c r="AI49" s="3" t="s">
-        <v>8</v>
+      <c r="AI49" s="3">
+        <v>900</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>8</v>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4982,17 +5102,17 @@
       <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
+      <c r="I52" s="3">
+        <v>100</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L52" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M52" s="3">
         <v>600</v>
@@ -5019,7 +5139,7 @@
         <v>600</v>
       </c>
       <c r="U52" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="V52" s="3">
         <v>900</v>
@@ -5031,7 +5151,7 @@
         <v>900</v>
       </c>
       <c r="Y52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="Z52" s="3">
         <v>1200</v>
@@ -5046,7 +5166,7 @@
         <v>1200</v>
       </c>
       <c r="AD52" s="3">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="AE52" s="3">
         <v>600</v>
@@ -5055,13 +5175,13 @@
         <v>600</v>
       </c>
       <c r="AG52" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AH52" s="3">
         <v>300</v>
       </c>
-      <c r="AI52" s="3" t="s">
-        <v>8</v>
+      <c r="AI52" s="3">
+        <v>300</v>
       </c>
       <c r="AJ52" s="3" t="s">
         <v>8</v>
@@ -5069,8 +5189,11 @@
       <c r="AK52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22600</v>
+      </c>
+      <c r="E54" s="3">
         <v>24800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>26200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>26400</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L54" s="3">
         <v>28800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>26000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25300</v>
-      </c>
-      <c r="P54" s="3">
-        <v>24900</v>
       </c>
       <c r="Q54" s="3">
         <v>24900</v>
       </c>
       <c r="R54" s="3">
+        <v>24900</v>
+      </c>
+      <c r="S54" s="3">
         <v>22200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>23000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>20800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>21100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>18800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>16700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>16900</v>
       </c>
-      <c r="AI54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,97 +5491,98 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
-      </c>
-      <c r="E57" s="3">
-        <v>1400</v>
       </c>
       <c r="F57" s="3">
         <v>1400</v>
       </c>
       <c r="G57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H57" s="3">
         <v>900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>800</v>
-      </c>
-      <c r="P57" s="3">
-        <v>900</v>
       </c>
       <c r="Q57" s="3">
         <v>900</v>
       </c>
       <c r="R57" s="3">
+        <v>900</v>
+      </c>
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1900</v>
-      </c>
-      <c r="V57" s="3">
-        <v>1400</v>
       </c>
       <c r="W57" s="3">
         <v>1400</v>
       </c>
       <c r="X57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Y57" s="3">
         <v>1000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1900</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>1300</v>
       </c>
       <c r="AB57" s="3">
         <v>1300</v>
       </c>
       <c r="AC57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AD57" s="3">
         <v>900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>500</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>700</v>
       </c>
       <c r="AG57" s="3">
         <v>700</v>
@@ -5459,8 +5590,8 @@
       <c r="AH57" s="3">
         <v>700</v>
       </c>
-      <c r="AI57" s="3" t="s">
-        <v>8</v>
+      <c r="AI57" s="3">
+        <v>700</v>
       </c>
       <c r="AJ57" s="3" t="s">
         <v>8</v>
@@ -5468,8 +5599,11 @@
       <c r="AK57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5480,26 +5614,26 @@
         <v>1700</v>
       </c>
       <c r="F58" s="3">
+        <v>1700</v>
+      </c>
+      <c r="G58" s="3">
         <v>1200</v>
-      </c>
-      <c r="G58" s="3">
-        <v>700</v>
       </c>
       <c r="H58" s="3">
         <v>700</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>600</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5521,14 +5655,14 @@
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>700</v>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
         <v>700</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>8</v>
+      <c r="V58" s="3">
+        <v>700</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>8</v>
@@ -5545,8 +5679,8 @@
       <c r="AA58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
@@ -5575,94 +5709,97 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E59" s="3">
         <v>1700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1300</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="3">
         <v>2300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1500</v>
       </c>
       <c r="Q59" s="3">
         <v>1500</v>
       </c>
       <c r="R59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S59" s="3">
         <v>1600</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1800</v>
       </c>
       <c r="T59" s="3">
         <v>1800</v>
       </c>
       <c r="U59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="V59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1900</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>1500</v>
       </c>
       <c r="Z59" s="3">
         <v>1500</v>
       </c>
       <c r="AA59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB59" s="3">
         <v>1400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1000</v>
-      </c>
-      <c r="AE59" s="3">
-        <v>1100</v>
       </c>
       <c r="AF59" s="3">
         <v>1100</v>
@@ -5671,156 +5808,162 @@
         <v>1100</v>
       </c>
       <c r="AH59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AI59" s="3">
         <v>1300</v>
       </c>
-      <c r="AI59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
         <v>5200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4200</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L60" s="3">
         <v>4800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2200</v>
-      </c>
-      <c r="P60" s="3">
-        <v>2400</v>
       </c>
       <c r="Q60" s="3">
         <v>2400</v>
       </c>
       <c r="R60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="S60" s="3">
         <v>2600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1600</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>1800</v>
       </c>
       <c r="AG60" s="3">
         <v>1800</v>
       </c>
       <c r="AH60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AI60" s="3">
         <v>2000</v>
       </c>
-      <c r="AI60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="E61" s="3">
         <v>1800</v>
       </c>
       <c r="F61" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G61" s="3">
         <v>2000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2300</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>2300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5840,16 +5983,16 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>1600</v>
-      </c>
-      <c r="T61" s="3">
-        <v>900</v>
       </c>
       <c r="U61" s="3">
         <v>900</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -5870,13 +6013,13 @@
         <v>0</v>
       </c>
       <c r="AC61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AD61" s="3">
         <v>500</v>
       </c>
       <c r="AE61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AF61" s="3">
         <v>0</v>
@@ -5896,83 +6039,86 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F62" s="3">
         <v>0</v>
       </c>
       <c r="G62" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>1400</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
+      <c r="I62" s="3">
+        <v>1400</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>2200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3100</v>
-      </c>
-      <c r="P62" s="3">
-        <v>3000</v>
       </c>
       <c r="Q62" s="3">
         <v>3000</v>
       </c>
       <c r="R62" s="3">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="S62" s="3">
         <v>400</v>
       </c>
       <c r="T62" s="3">
+        <v>400</v>
+      </c>
+      <c r="U62" s="3">
         <v>500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>900</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>8</v>
       </c>
@@ -5985,8 +6131,8 @@
       <c r="AE62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF62" s="3">
-        <v>0</v>
+      <c r="AF62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG62" s="3">
         <v>0</v>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,8 +6479,11 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6333,106 +6491,109 @@
         <v>7000</v>
       </c>
       <c r="E66" s="3">
-        <v>8100</v>
+        <v>7000</v>
       </c>
       <c r="F66" s="3">
         <v>8100</v>
       </c>
       <c r="G66" s="3">
+        <v>8100</v>
+      </c>
+      <c r="H66" s="3">
         <v>8400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7900</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L66" s="3">
         <v>9300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5200</v>
-      </c>
-      <c r="P66" s="3">
-        <v>5400</v>
       </c>
       <c r="Q66" s="3">
         <v>5400</v>
       </c>
       <c r="R66" s="3">
+        <v>5400</v>
+      </c>
+      <c r="S66" s="3">
         <v>3000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>4200</v>
-      </c>
-      <c r="W66" s="3">
-        <v>4000</v>
       </c>
       <c r="X66" s="3">
         <v>4000</v>
       </c>
       <c r="Y66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Z66" s="3">
         <v>3400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>4200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1600</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>1800</v>
       </c>
       <c r="AG66" s="3">
         <v>1800</v>
       </c>
       <c r="AH66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AI66" s="3">
         <v>2000</v>
       </c>
-      <c r="AI66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E72" s="3">
         <v>1500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2200</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>2800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3000</v>
-      </c>
-      <c r="P72" s="3">
-        <v>2300</v>
       </c>
       <c r="Q72" s="3">
         <v>2300</v>
       </c>
       <c r="R72" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S72" s="3">
         <v>1800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-500</v>
-      </c>
-      <c r="X72" s="3">
-        <v>-300</v>
       </c>
       <c r="Y72" s="3">
         <v>-300</v>
       </c>
       <c r="Z72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E76" s="3">
         <v>17800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>18100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18500</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L76" s="3">
         <v>19500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20100</v>
-      </c>
-      <c r="P76" s="3">
-        <v>19500</v>
       </c>
       <c r="Q76" s="3">
         <v>19500</v>
       </c>
       <c r="R76" s="3">
+        <v>19500</v>
+      </c>
+      <c r="S76" s="3">
         <v>19200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>17400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17100</v>
-      </c>
-      <c r="X76" s="3">
-        <v>17500</v>
       </c>
       <c r="Y76" s="3">
         <v>17500</v>
       </c>
       <c r="Z76" s="3">
+        <v>17500</v>
+      </c>
+      <c r="AA76" s="3">
         <v>16900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>16300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14800</v>
       </c>
-      <c r="AI76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AK76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
-      </c>
-      <c r="K80" s="2">
-        <v>44834</v>
       </c>
       <c r="L80" s="2">
         <v>44834</v>
       </c>
       <c r="M80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>-300</v>
       </c>
       <c r="L81" s="3">
         <v>-300</v>
       </c>
       <c r="M81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,25 +7996,26 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>200</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
-        <v>100</v>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
+      <c r="H83" s="3">
+        <v>100</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>8</v>
@@ -7827,15 +8026,15 @@
       <c r="K83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -7848,8 +8047,8 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>8</v>
@@ -7866,20 +8065,20 @@
       <c r="X83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB83" s="3">
         <v>100</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -7905,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,8 +8654,11 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8451,75 +8668,75 @@
       <c r="E89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>-1500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>700</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M89" s="3">
         <v>-800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3700</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC89" s="3" t="s">
         <v>8</v>
       </c>
@@ -8529,8 +8746,8 @@
       <c r="AE89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
+      <c r="AF89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG89" s="3">
         <v>0</v>
@@ -8547,8 +8764,11 @@
       <c r="AK89" s="3">
         <v>0</v>
       </c>
+      <c r="AL89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8597,26 +8818,26 @@
       <c r="E91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
+      <c r="H91" s="3">
+        <v>0</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -8657,17 +8878,17 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -8693,8 +8914,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,8 +9134,11 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8918,29 +9148,29 @@
       <c r="E94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -8978,17 +9208,17 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB94" s="3">
         <v>100</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -9014,8 +9244,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9064,26 +9298,26 @@
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
+      <c r="H96" s="3">
+        <v>0</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>100</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,8 +9724,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9492,29 +9738,29 @@
       <c r="E100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>8</v>
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N100" s="3">
         <v>0</v>
@@ -9552,17 +9798,17 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-300</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>0</v>
+      <c r="AC100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
@@ -9588,8 +9834,11 @@
       <c r="AK100" s="3">
         <v>0</v>
       </c>
+      <c r="AL100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9617,8 +9866,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9695,8 +9944,11 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9707,28 +9959,28 @@
         <v>0</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-1400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M102" s="3">
-        <v>0</v>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N102" s="3">
         <v>0</v>
@@ -9766,17 +10018,17 @@
       <c r="Y102" s="3">
         <v>0</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB102" s="3">
         <v>3600</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>0</v>
+      <c r="AC102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD102" s="3">
         <v>0</v>
@@ -9800,6 +10052,9 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="92">
   <si>
     <t>ORBT</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
-      </c>
-      <c r="L7" s="2">
-        <v>44834</v>
       </c>
       <c r="M7" s="2">
         <v>44834</v>
       </c>
       <c r="N7" s="2">
+        <v>44834</v>
+      </c>
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3">
         <v>4700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8700</v>
       </c>
-      <c r="F8" s="3">
-        <v>8400</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3">
         <v>6600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7000</v>
-      </c>
-      <c r="L8" s="3">
-        <v>6000</v>
       </c>
       <c r="M8" s="3">
         <v>6000</v>
       </c>
       <c r="N8" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O8" s="3">
         <v>5800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>24700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>20900</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>5000</v>
       </c>
       <c r="AH8" s="3">
         <v>5000</v>
       </c>
       <c r="AI8" s="3">
+        <v>5000</v>
+      </c>
+      <c r="AJ8" s="3">
         <v>5200</v>
-      </c>
-      <c r="AJ8" s="3">
-        <v>5500</v>
       </c>
       <c r="AK8" s="3">
         <v>5500</v>
       </c>
       <c r="AL8" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AM8" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
         <v>4100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5700</v>
       </c>
-      <c r="F9" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3">
         <v>4700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4300</v>
-      </c>
-      <c r="I9" s="3">
-        <v>5000</v>
       </c>
       <c r="J9" s="3">
         <v>5000</v>
       </c>
       <c r="K9" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L9" s="3">
         <v>4700</v>
-      </c>
-      <c r="L9" s="3">
-        <v>4100</v>
       </c>
       <c r="M9" s="3">
         <v>4100</v>
       </c>
       <c r="N9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O9" s="3">
         <v>4200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>16500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2900</v>
-      </c>
-      <c r="AH9" s="3">
-        <v>3200</v>
       </c>
       <c r="AI9" s="3">
         <v>3200</v>
       </c>
       <c r="AJ9" s="3">
+        <v>3200</v>
+      </c>
+      <c r="AK9" s="3">
         <v>3300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3300</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3">
         <v>600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3000</v>
       </c>
-      <c r="F10" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1900</v>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H10" s="3">
         <v>1900</v>
       </c>
       <c r="I10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J10" s="3">
         <v>2200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2200</v>
-      </c>
-      <c r="S10" s="3">
-        <v>1700</v>
       </c>
       <c r="T10" s="3">
         <v>1700</v>
       </c>
       <c r="U10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V10" s="3">
         <v>2500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>8200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>8200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1600</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,8 +1205,8 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
+      <c r="F12" s="3">
+        <v>2300</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1203,8 +1217,8 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="J12" s="3">
+        <v>1900</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1423,14 +1443,14 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3">
+        <v>100</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1439,41 +1459,41 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-1600</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1489,8 +1509,8 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1501,8 +1521,8 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
+      <c r="AJ14" s="3">
+        <v>0</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
@@ -1510,28 +1530,31 @@
       <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>100</v>
       </c>
-      <c r="F15" s="3">
-        <v>200</v>
-      </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
@@ -1540,7 +1563,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,37 +1683,38 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
         <v>6900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8400</v>
       </c>
-      <c r="F17" s="3">
-        <v>7800</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3">
         <v>7200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7100</v>
-      </c>
-      <c r="L17" s="3">
-        <v>6300</v>
       </c>
       <c r="M17" s="3">
         <v>6300</v>
@@ -1696,189 +1723,195 @@
         <v>6300</v>
       </c>
       <c r="O17" s="3">
+        <v>6300</v>
+      </c>
+      <c r="P17" s="3">
         <v>6400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>6700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>23000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>19300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>300</v>
       </c>
-      <c r="F18" s="3">
-        <v>600</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-300</v>
       </c>
       <c r="M18" s="3">
         <v>-300</v>
       </c>
       <c r="N18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O18" s="3">
         <v>-500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-200</v>
       </c>
-      <c r="Y18" s="3">
-        <v>0</v>
-      </c>
       <c r="Z18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="3">
         <v>600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,49 +1950,50 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
+        <v>400</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1974,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
         <v>-100</v>
@@ -1983,7 +2017,7 @@
         <v>-100</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -2007,11 +2041,11 @@
         <v>0</v>
       </c>
       <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
@@ -2027,89 +2061,92 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2000</v>
       </c>
-      <c r="E21" s="3">
-        <v>400</v>
-      </c>
       <c r="F21" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
         <v>0</v>
       </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
-        <v>-200</v>
-      </c>
       <c r="J21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K21" s="3">
         <v>900</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-300</v>
       </c>
       <c r="L21" s="3">
         <v>-300</v>
       </c>
       <c r="M21" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="N21" s="3">
         <v>-200</v>
       </c>
       <c r="O21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P21" s="3">
         <v>500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-100</v>
       </c>
-      <c r="Y21" s="3">
-        <v>0</v>
-      </c>
       <c r="Z21" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="3">
         <v>600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1800</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>8</v>
       </c>
@@ -2137,22 +2174,25 @@
       <c r="AL21" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM21" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -2166,20 +2206,20 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2187,11 +2227,11 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -2199,11 +2239,11 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -2211,11 +2251,11 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2223,11 +2263,11 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-      <c r="AE22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
@@ -2247,132 +2287,138 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>200</v>
       </c>
-      <c r="F23" s="3">
-        <v>600</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="I23" s="3">
-        <v>-300</v>
-      </c>
       <c r="J23" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-400</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-300</v>
       </c>
       <c r="M23" s="3">
         <v>-300</v>
       </c>
       <c r="N23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O23" s="3">
         <v>-400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-400</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-200</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
       <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E24" s="3">
-        <v>500</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>400</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -2435,40 +2481,43 @@
         <v>0</v>
       </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-500</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-600</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-300</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
       <c r="AI24" s="3">
         <v>0</v>
       </c>
       <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="3">
         <v>-300</v>
       </c>
-      <c r="AK24" s="3">
-        <v>0</v>
-      </c>
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
-        <v>600</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-500</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-300</v>
       </c>
       <c r="M26" s="3">
         <v>-300</v>
       </c>
       <c r="N26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-400</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-200</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
       <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
-        <v>600</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-500</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-300</v>
       </c>
       <c r="M27" s="3">
         <v>-300</v>
       </c>
       <c r="N27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-400</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-200</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,49 +3304,52 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3294,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V32" s="3">
         <v>100</v>
@@ -3303,7 +3373,7 @@
         <v>100</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
@@ -3327,11 +3397,11 @@
         <v>0</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
@@ -3347,118 +3417,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
-        <v>600</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-500</v>
-      </c>
-      <c r="L33" s="3">
-        <v>-300</v>
       </c>
       <c r="M33" s="3">
         <v>-300</v>
       </c>
       <c r="N33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-400</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-200</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
       <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
-        <v>600</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-500</v>
-      </c>
-      <c r="L35" s="3">
-        <v>-300</v>
       </c>
       <c r="M35" s="3">
         <v>-300</v>
       </c>
       <c r="N35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-400</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-200</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
       <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
-      </c>
-      <c r="L38" s="2">
-        <v>44834</v>
       </c>
       <c r="M38" s="2">
         <v>44834</v>
       </c>
       <c r="N38" s="2">
+        <v>44834</v>
+      </c>
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
         <v>700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="F41" s="3">
-        <v>300</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" s="3">
         <v>500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M41" s="3">
         <v>3400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8300</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>6900</v>
       </c>
       <c r="R41" s="3">
         <v>6900</v>
       </c>
       <c r="S41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="T41" s="3">
         <v>7000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1100</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>900</v>
       </c>
       <c r="AF41" s="3">
         <v>900</v>
       </c>
       <c r="AG41" s="3">
+        <v>900</v>
+      </c>
+      <c r="AH41" s="3">
         <v>800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1900</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK41" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL41" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM41" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4072,19 +4162,19 @@
         <v>0</v>
       </c>
       <c r="AF42" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG42" s="3">
         <v>300</v>
       </c>
       <c r="AH42" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AI42" s="3">
         <v>200</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>8</v>
+      <c r="AJ42" s="3">
+        <v>200</v>
       </c>
       <c r="AK42" s="3" t="s">
         <v>8</v>
@@ -4092,70 +4182,73 @@
       <c r="AL42" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM42" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
         <v>3200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4600</v>
       </c>
-      <c r="F43" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3">
         <v>4300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="3">
         <v>4000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3300</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>3700</v>
       </c>
       <c r="R43" s="3">
         <v>3700</v>
       </c>
       <c r="S43" s="3">
+        <v>3700</v>
+      </c>
+      <c r="T43" s="3">
         <v>3300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3700</v>
-      </c>
-      <c r="W43" s="3">
-        <v>3800</v>
       </c>
       <c r="X43" s="3">
         <v>3800</v>
@@ -4164,138 +4257,141 @@
         <v>3800</v>
       </c>
       <c r="Z43" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA43" s="3">
         <v>3700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>3800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>4300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>3000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK43" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL43" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>9100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>8900</v>
       </c>
-      <c r="F44" s="3">
-        <v>10400</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3">
         <v>10300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3">
         <v>10600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>11800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8400</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>9000</v>
       </c>
       <c r="R44" s="3">
         <v>9000</v>
       </c>
       <c r="S44" s="3">
-        <v>9400</v>
+        <v>9000</v>
       </c>
       <c r="T44" s="3">
         <v>9400</v>
       </c>
       <c r="U44" s="3">
+        <v>9400</v>
+      </c>
+      <c r="V44" s="3">
         <v>10000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>10800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>11200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>10500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>10300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>10000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>10700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>10100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>11400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>10900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>9600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>10100</v>
-      </c>
-      <c r="AG44" s="3">
-        <v>10000</v>
       </c>
       <c r="AH44" s="3">
         <v>10000</v>
@@ -4303,8 +4399,8 @@
       <c r="AI44" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>8</v>
+      <c r="AJ44" s="3">
+        <v>10000</v>
       </c>
       <c r="AK44" s="3" t="s">
         <v>8</v>
@@ -4312,13 +4408,16 @@
       <c r="AL44" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM44" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>400</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
@@ -4326,26 +4425,26 @@
       <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>1000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>400</v>
       </c>
       <c r="N45" s="3">
         <v>400</v>
@@ -4357,19 +4456,19 @@
         <v>400</v>
       </c>
       <c r="Q45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R45" s="3">
         <v>300</v>
       </c>
       <c r="S45" s="3">
+        <v>300</v>
+      </c>
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
-      </c>
-      <c r="U45" s="3">
-        <v>400</v>
       </c>
       <c r="V45" s="3">
         <v>400</v>
@@ -4378,16 +4477,16 @@
         <v>400</v>
       </c>
       <c r="X45" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y45" s="3">
         <v>300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>200</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>300</v>
       </c>
       <c r="AB45" s="3">
         <v>300</v>
@@ -4396,144 +4495,150 @@
         <v>300</v>
       </c>
       <c r="AD45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE45" s="3">
         <v>900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>300</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL45" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM45" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
         <v>13300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>15200</v>
       </c>
-      <c r="F46" s="3">
-        <v>16400</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" s="3">
         <v>15500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>15800</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M46" s="3">
         <v>19000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>21300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>21100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20400</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>19800</v>
       </c>
       <c r="R46" s="3">
         <v>19800</v>
       </c>
       <c r="S46" s="3">
+        <v>19800</v>
+      </c>
+      <c r="T46" s="3">
         <v>20100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>20600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>19300</v>
-      </c>
-      <c r="W46" s="3">
-        <v>18200</v>
       </c>
       <c r="X46" s="3">
         <v>18200</v>
       </c>
       <c r="Y46" s="3">
+        <v>18200</v>
+      </c>
+      <c r="Z46" s="3">
         <v>18500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>15300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>15400</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK46" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL46" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM46" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4642,85 +4747,88 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>3300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3600</v>
       </c>
-      <c r="F48" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" s="3">
         <v>3600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3900</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L48" s="3">
-        <v>3300</v>
+      <c r="L48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M48" s="3">
         <v>3300</v>
       </c>
       <c r="N48" s="3">
+        <v>3300</v>
+      </c>
+      <c r="O48" s="3">
         <v>3400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3400</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>3600</v>
       </c>
       <c r="R48" s="3">
         <v>3600</v>
       </c>
       <c r="S48" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T48" s="3">
         <v>700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1000</v>
-      </c>
-      <c r="V48" s="3">
-        <v>1100</v>
       </c>
       <c r="W48" s="3">
         <v>1100</v>
       </c>
       <c r="X48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Y48" s="3">
         <v>1200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB48" s="3">
-        <v>300</v>
       </c>
       <c r="AC48" s="3">
         <v>300</v>
@@ -4732,7 +4840,7 @@
         <v>300</v>
       </c>
       <c r="AF48" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AG48" s="3">
         <v>200</v>
@@ -4741,57 +4849,60 @@
         <v>200</v>
       </c>
       <c r="AI48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AJ48" s="3">
         <v>300</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL48" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM48" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>5800</v>
+      <c r="D49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E49" s="3">
         <v>5800</v>
       </c>
       <c r="F49" s="3">
-        <v>5900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>6000</v>
+        <v>5800</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H49" s="3">
         <v>6000</v>
       </c>
       <c r="I49" s="3">
+        <v>6000</v>
+      </c>
+      <c r="J49" s="3">
         <v>6100</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
       <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>5900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>6000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>900</v>
       </c>
       <c r="P49" s="3">
         <v>900</v>
@@ -4853,8 +4964,8 @@
       <c r="AI49" s="3">
         <v>900</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>8</v>
+      <c r="AJ49" s="3">
+        <v>900</v>
       </c>
       <c r="AK49" s="3" t="s">
         <v>8</v>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,13 +5199,16 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>100</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
@@ -5096,8 +5216,8 @@
       <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
-        <v>100</v>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -5105,17 +5225,17 @@
       <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
+      <c r="J52" s="3">
+        <v>100</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M52" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>600</v>
@@ -5142,7 +5262,7 @@
         <v>600</v>
       </c>
       <c r="V52" s="3">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="W52" s="3">
         <v>900</v>
@@ -5154,7 +5274,7 @@
         <v>900</v>
       </c>
       <c r="Z52" s="3">
-        <v>1200</v>
+        <v>900</v>
       </c>
       <c r="AA52" s="3">
         <v>1200</v>
@@ -5169,7 +5289,7 @@
         <v>1200</v>
       </c>
       <c r="AE52" s="3">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="AF52" s="3">
         <v>600</v>
@@ -5178,13 +5298,13 @@
         <v>600</v>
       </c>
       <c r="AH52" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AI52" s="3">
         <v>300</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>8</v>
+      <c r="AJ52" s="3">
+        <v>300</v>
       </c>
       <c r="AK52" s="3" t="s">
         <v>8</v>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
         <v>22600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>24800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" s="3">
+        <v>25700</v>
+      </c>
+      <c r="I54" s="3">
         <v>26200</v>
       </c>
-      <c r="G54" s="3">
-        <v>25700</v>
-      </c>
-      <c r="H54" s="3">
-        <v>26200</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>26400</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M54" s="3">
         <v>28800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25300</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>24900</v>
       </c>
       <c r="R54" s="3">
         <v>24900</v>
       </c>
       <c r="S54" s="3">
+        <v>24900</v>
+      </c>
+      <c r="T54" s="3">
         <v>22200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>23000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>22100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>21000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>21500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>20800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>19700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>18800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>17700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>16400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>16000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>16700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>16900</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK54" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL54" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM54" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,100 +5622,101 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="G57" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>800</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>900</v>
       </c>
       <c r="R57" s="3">
         <v>900</v>
       </c>
       <c r="S57" s="3">
+        <v>900</v>
+      </c>
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1900</v>
-      </c>
-      <c r="W57" s="3">
-        <v>1400</v>
       </c>
       <c r="X57" s="3">
         <v>1400</v>
       </c>
       <c r="Y57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z57" s="3">
         <v>1000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1900</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>1300</v>
       </c>
       <c r="AC57" s="3">
         <v>1300</v>
       </c>
       <c r="AD57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>500</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>700</v>
       </c>
       <c r="AH57" s="3">
         <v>700</v>
@@ -5593,8 +5724,8 @@
       <c r="AI57" s="3">
         <v>700</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>8</v>
+      <c r="AJ57" s="3">
+        <v>700</v>
       </c>
       <c r="AK57" s="3" t="s">
         <v>8</v>
@@ -5602,13 +5733,16 @@
       <c r="AL57" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM57" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>1700</v>
+      <c r="D58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E58" s="3">
         <v>1700</v>
@@ -5616,27 +5750,27 @@
       <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H58" s="3">
         <v>1200</v>
-      </c>
-      <c r="H58" s="3">
-        <v>700</v>
       </c>
       <c r="I58" s="3">
         <v>700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>600</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
@@ -5658,14 +5792,14 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
-        <v>700</v>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3">
         <v>700</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>8</v>
+      <c r="W58" s="3">
+        <v>700</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>8</v>
@@ -5682,8 +5816,8 @@
       <c r="AB58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -5712,97 +5846,100 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>1600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
-        <v>2100</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" s="3">
         <v>2400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1300</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="L59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M59" s="3">
         <v>2300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1500</v>
       </c>
       <c r="R59" s="3">
         <v>1500</v>
       </c>
       <c r="S59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T59" s="3">
         <v>1600</v>
-      </c>
-      <c r="T59" s="3">
-        <v>1800</v>
       </c>
       <c r="U59" s="3">
         <v>1800</v>
       </c>
       <c r="V59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="W59" s="3">
         <v>1700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1900</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>1500</v>
       </c>
       <c r="AA59" s="3">
         <v>1500</v>
       </c>
       <c r="AB59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AC59" s="3">
         <v>1400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1000</v>
-      </c>
-      <c r="AF59" s="3">
-        <v>1100</v>
       </c>
       <c r="AG59" s="3">
         <v>1100</v>
@@ -5811,162 +5948,168 @@
         <v>1100</v>
       </c>
       <c r="AI59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK59" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL59" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM59" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
         <v>5400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5200</v>
       </c>
-      <c r="F60" s="3">
-        <v>6300</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H60" s="3">
         <v>6100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4200</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M60" s="3">
         <v>4800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2200</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>2400</v>
       </c>
       <c r="R60" s="3">
         <v>2400</v>
       </c>
       <c r="S60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="T60" s="3">
         <v>2600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1600</v>
-      </c>
-      <c r="AG60" s="3">
-        <v>1800</v>
       </c>
       <c r="AH60" s="3">
         <v>1800</v>
       </c>
       <c r="AI60" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK60" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL60" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM60" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>1600</v>
-      </c>
-      <c r="E61" s="3">
-        <v>1800</v>
       </c>
       <c r="F61" s="3">
         <v>1800</v>
       </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>2000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2300</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>2300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5986,16 +6129,16 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>1600</v>
-      </c>
-      <c r="U61" s="3">
-        <v>900</v>
       </c>
       <c r="V61" s="3">
         <v>900</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -6016,13 +6159,13 @@
         <v>0</v>
       </c>
       <c r="AD61" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AE61" s="3">
         <v>500</v>
       </c>
       <c r="AF61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AG61" s="3">
         <v>0</v>
@@ -6042,8 +6185,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6053,75 +6199,75 @@
       <c r="E62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H62" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3">
         <v>1400</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
+      <c r="J62" s="3">
+        <v>1400</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>2200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3100</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>3000</v>
       </c>
       <c r="R62" s="3">
         <v>3000</v>
       </c>
       <c r="S62" s="3">
-        <v>400</v>
+        <v>3000</v>
       </c>
       <c r="T62" s="3">
         <v>400</v>
       </c>
       <c r="U62" s="3">
+        <v>400</v>
+      </c>
+      <c r="V62" s="3">
         <v>500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>900</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>8</v>
       </c>
@@ -6134,8 +6280,8 @@
       <c r="AF62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG62" s="3">
-        <v>0</v>
+      <c r="AG62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH62" s="3">
         <v>0</v>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>7000</v>
+      <c r="D66" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E66" s="3">
         <v>7000</v>
       </c>
       <c r="F66" s="3">
+        <v>7000</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H66" s="3">
         <v>8100</v>
       </c>
-      <c r="G66" s="3">
-        <v>8100</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M66" s="3">
         <v>9300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5200</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>5400</v>
       </c>
       <c r="R66" s="3">
         <v>5400</v>
       </c>
       <c r="S66" s="3">
+        <v>5400</v>
+      </c>
+      <c r="T66" s="3">
         <v>3000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>4200</v>
-      </c>
-      <c r="X66" s="3">
-        <v>4000</v>
       </c>
       <c r="Y66" s="3">
         <v>4000</v>
       </c>
       <c r="Z66" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA66" s="3">
         <v>3400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>4200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1600</v>
-      </c>
-      <c r="AG66" s="3">
-        <v>1800</v>
       </c>
       <c r="AH66" s="3">
         <v>1800</v>
       </c>
       <c r="AI66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK66" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL66" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM66" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>-700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1500</v>
       </c>
-      <c r="F72" s="3">
-        <v>1700</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3">
         <v>1200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2200</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>2800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3000</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>2300</v>
       </c>
       <c r="R72" s="3">
         <v>2300</v>
       </c>
       <c r="S72" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T72" s="3">
         <v>1800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-1100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-500</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>-300</v>
       </c>
       <c r="Z72" s="3">
         <v>-300</v>
       </c>
       <c r="AA72" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AB72" s="3">
         <v>-800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-4700</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL72" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM72" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>15600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17800</v>
       </c>
-      <c r="F76" s="3">
-        <v>18100</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H76" s="3">
         <v>17500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18500</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M76" s="3">
         <v>19500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20100</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>19500</v>
       </c>
       <c r="R76" s="3">
         <v>19500</v>
       </c>
       <c r="S76" s="3">
+        <v>19500</v>
+      </c>
+      <c r="T76" s="3">
         <v>19200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>17400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>17200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17100</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>17500</v>
       </c>
       <c r="Z76" s="3">
         <v>17500</v>
       </c>
       <c r="AA76" s="3">
+        <v>17500</v>
+      </c>
+      <c r="AB76" s="3">
         <v>16900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>16800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>16300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14800</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK76" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AL76" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM76" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
-      </c>
-      <c r="L80" s="2">
-        <v>44834</v>
       </c>
       <c r="M80" s="2">
         <v>44834</v>
       </c>
       <c r="N80" s="2">
+        <v>44834</v>
+      </c>
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
-        <v>600</v>
-      </c>
-      <c r="G81" s="3">
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-500</v>
-      </c>
-      <c r="L81" s="3">
-        <v>-300</v>
       </c>
       <c r="M81" s="3">
         <v>-300</v>
       </c>
       <c r="N81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-400</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-200</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
       <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,28 +8195,29 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
+      <c r="E83" s="3">
+        <v>300</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G83" s="3">
-        <v>100</v>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
+      <c r="I83" s="3">
+        <v>100</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>8</v>
@@ -8029,15 +8228,15 @@
       <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N83" s="3">
         <v>100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -8050,8 +8249,8 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>8</v>
@@ -8068,20 +8267,20 @@
       <c r="Y83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC83" s="3">
         <v>100</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>0</v>
+      <c r="AD83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,89 +8871,92 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
+      <c r="E89" s="3">
+        <v>-600</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>700</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3700</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>8</v>
       </c>
@@ -8749,8 +8966,8 @@
       <c r="AF89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG89" s="3">
-        <v>0</v>
+      <c r="AG89" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH89" s="3">
         <v>0</v>
@@ -8767,8 +8984,11 @@
       <c r="AL89" s="3">
         <v>0</v>
       </c>
+      <c r="AM89" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,40 +9027,41 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
+      <c r="E91" s="3">
+        <v>-100</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
+      <c r="I91" s="3">
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -8881,17 +9102,17 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -8917,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,43 +9364,46 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
+      <c r="E94" s="3">
+        <v>-100</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="N94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -9211,17 +9441,17 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC94" s="3">
         <v>100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AD94" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
@@ -9247,8 +9477,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9301,26 +9535,26 @@
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
+      <c r="I96" s="3">
+        <v>0</v>
       </c>
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>100</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,43 +9970,46 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
+      <c r="E100" s="3">
+        <v>0</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>8</v>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="N100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -9801,17 +10047,17 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-300</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
+      <c r="AD100" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
@@ -9837,8 +10083,11 @@
       <c r="AL100" s="3">
         <v>0</v>
       </c>
+      <c r="AM100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9869,8 +10118,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9947,8 +10196,11 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9956,34 +10208,34 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>600</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1600</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
@@ -10021,17 +10273,17 @@
       <c r="Z102" s="3">
         <v>0</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC102" s="3">
         <v>3600</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD102" s="3">
-        <v>0</v>
+      <c r="AD102" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE102" s="3">
         <v>0</v>
@@ -10055,6 +10307,9 @@
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>0</v>
       </c>
     </row>
